--- a/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_12_43.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_12_43.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3447401.367889231</v>
+        <v>3448528.192956977</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13605742.17777128</v>
+        <v>13604525.51577222</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13605742.17777128</v>
+        <v>13604525.51577222</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>134988.5924107684</v>
+        <v>132340.8186286054</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>134988.5924107684</v>
+        <v>132340.8186286054</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24188655.41529977</v>
+        <v>24189520.5854729</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557451</v>
+        <v>81.99931295557316</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
@@ -669,10 +669,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>5.447406888511121</v>
+        <v>3.343301935257416</v>
       </c>
       <c r="H2" t="n">
-        <v>3.727889859306304</v>
+        <v>3.769060713577661</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -702,16 +702,16 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.953406460792953</v>
       </c>
       <c r="S2" t="n">
-        <v>85.32093162141838</v>
+        <v>85.41253966161939</v>
       </c>
       <c r="T2" t="n">
-        <v>184.84539077379</v>
+        <v>184.8629887637398</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1878493124298</v>
+        <v>249.18817092047</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
@@ -748,13 +748,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5158377618198</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0076343562325</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,19 +778,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>144.5243971659513</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
-        <v>133.3848916320019</v>
+        <v>272.4580145469999</v>
       </c>
       <c r="S3" t="n">
-        <v>62.40890562498866</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T3" t="n">
-        <v>4.456104840155326</v>
+        <v>4.46477465147608</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1956427790546723</v>
+        <v>0.1957842884886345</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>41.50713907114702</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.23370976320562</v>
+        <v>91.51638189435316</v>
       </c>
       <c r="N4" t="n">
-        <v>142.4861900257833</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O4" t="n">
-        <v>213.9374985052445</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P4" t="n">
-        <v>264.7656678200808</v>
+        <v>264.9837661807365</v>
       </c>
       <c r="Q4" t="n">
-        <v>310.135266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>318.1696033909871</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -912,7 +912,7 @@
         <v>3.727889859306288</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2.108125053756234</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.108125053756319</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>85.32093162141837</v>
@@ -973,16 +973,16 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>287.2286772425882</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>209.4244990988957</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>144.5243971659513</v>
       </c>
       <c r="R6" t="n">
         <v>133.3848916320019</v>
@@ -1036,10 +1036,10 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>19.86273944538755</v>
+        <v>374</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>324.4655354109802</v>
       </c>
     </row>
     <row r="7">
@@ -1146,7 +1146,7 @@
         <v>3.3392818347549</v>
       </c>
       <c r="H8" t="n">
-        <v>3.727889859306288</v>
+        <v>5.836014913062525</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
         <v>249.1878493124298</v>
       </c>
       <c r="V8" t="n">
-        <v>231.9591492205801</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W8" t="n">
         <v>238.3734759809475</v>
@@ -1219,10 +1219,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.5158377618198</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1252,10 +1252,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>144.5243971659513</v>
       </c>
       <c r="R9" t="n">
-        <v>304.5222302116659</v>
+        <v>374</v>
       </c>
       <c r="S9" t="n">
         <v>62.40890562498868</v>
@@ -1267,13 +1267,13 @@
         <v>0.1956427790546513</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>374</v>
       </c>
       <c r="W9" t="n">
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>111.5233197823188</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1380,10 +1380,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>81.35435721163935</v>
+        <v>81.35435721163932</v>
       </c>
       <c r="H11" t="n">
-        <v>72.64103056282391</v>
+        <v>72.6410305628239</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1447,10 +1447,10 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C12" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D12" t="n">
-        <v>216.4752542749595</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
         <v>21.67209722191262</v>
@@ -1459,10 +1459,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>324.9888566297443</v>
+        <v>3.988856629744324</v>
       </c>
       <c r="H12" t="n">
-        <v>3.918106054345685</v>
+        <v>3.918106054345659</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1498,10 +1498,10 @@
         <v>131.6204622287622</v>
       </c>
       <c r="T12" t="n">
-        <v>81.3320010665704</v>
+        <v>81.33200106657043</v>
       </c>
       <c r="U12" t="n">
-        <v>400.1609729677339</v>
+        <v>79.16097296773391</v>
       </c>
       <c r="V12" t="n">
         <v>93.51066719152016</v>
@@ -1510,7 +1510,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>98.86273944538755</v>
+        <v>288.4003068226444</v>
       </c>
       <c r="Y12" t="n">
         <v>78.39139276613435</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>8.981300288926718</v>
+        <v>8.981300288926704</v>
       </c>
       <c r="M13" t="n">
         <v>100.9790376320581</v>
@@ -1574,7 +1574,7 @@
         <v>377.304521423774</v>
       </c>
       <c r="S13" t="n">
-        <v>30.40572560449476</v>
+        <v>30.40572560449478</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1617,10 +1617,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>82.5885375417771</v>
+        <v>81.35435721163935</v>
       </c>
       <c r="H14" t="n">
-        <v>72.64103056282391</v>
+        <v>73.87521089296166</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1681,19 +1681,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C15" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E15" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
         <v>3.988856629744305</v>
@@ -1747,10 +1747,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>288.4003068226442</v>
+        <v>288.4003068226444</v>
       </c>
       <c r="Y15" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -1860,7 +1860,7 @@
         <v>72.64103056282391</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1.234180330137742</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.234180330137756</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>141.8769617721721</v>
@@ -1930,7 +1930,7 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>208.1738097151335</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G18" t="n">
         <v>3.988856629744305</v>
@@ -1981,7 +1981,7 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W18" t="n">
-        <v>111.3731429098285</v>
+        <v>300.9107102870851</v>
       </c>
       <c r="X18" t="n">
         <v>419.8627394453875</v>
@@ -2091,10 +2091,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>81.35435721163935</v>
+        <v>81.35435721163932</v>
       </c>
       <c r="H20" t="n">
-        <v>72.64103056282391</v>
+        <v>72.6410305628239</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2164,16 +2164,16 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F21" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G21" t="n">
-        <v>3.988856629744305</v>
+        <v>3.988856629744324</v>
       </c>
       <c r="H21" t="n">
-        <v>193.4556734316025</v>
+        <v>3.918106054345659</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2209,22 +2209,22 @@
         <v>131.6204622287622</v>
       </c>
       <c r="T21" t="n">
-        <v>81.3320010665704</v>
+        <v>81.33200106657043</v>
       </c>
       <c r="U21" t="n">
-        <v>79.16097296773393</v>
+        <v>79.16097296773391</v>
       </c>
       <c r="V21" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>111.3731429098285</v>
+        <v>300.9107102870851</v>
       </c>
       <c r="X21" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y21" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="22">
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>8.981300288926718</v>
+        <v>8.981300288926704</v>
       </c>
       <c r="M22" t="n">
         <v>100.9790376320581</v>
@@ -2285,7 +2285,7 @@
         <v>377.304521423774</v>
       </c>
       <c r="S22" t="n">
-        <v>30.40572560449476</v>
+        <v>30.40572560449478</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2395,22 +2395,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>40.09991244551929</v>
+        <v>229.637479822776</v>
       </c>
       <c r="D24" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>208.1738097151338</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>3.988856629744305</v>
       </c>
       <c r="H24" t="n">
-        <v>324.9181060543457</v>
+        <v>3.918106054345685</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2449,10 +2449,10 @@
         <v>81.3320010665704</v>
       </c>
       <c r="U24" t="n">
-        <v>400.1609729677339</v>
+        <v>79.16097296773393</v>
       </c>
       <c r="V24" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
         <v>111.3731429098285</v>
@@ -2550,25 +2550,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>161.9993129555745</v>
+        <v>160.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>120.5895585731338</v>
+        <v>128.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>90.33915573984979</v>
+        <v>89.33915573984979</v>
       </c>
       <c r="E26" t="n">
-        <v>84.36328960686865</v>
+        <v>88.4782699370064</v>
       </c>
       <c r="F26" t="n">
-        <v>84.88962870801186</v>
+        <v>83.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>82.35435721163932</v>
+        <v>81.35435721163935</v>
       </c>
       <c r="H26" t="n">
-        <v>73.6410305628239</v>
+        <v>72.64103056282391</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2601,25 +2601,25 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>142.8769617721721</v>
+        <v>141.8769617721721</v>
       </c>
       <c r="T26" t="n">
-        <v>260.5338832361016</v>
+        <v>259.5338832361016</v>
       </c>
       <c r="U26" t="n">
-        <v>329.1090553425805</v>
+        <v>328.1090553425805</v>
       </c>
       <c r="V26" t="n">
-        <v>309.8510241668239</v>
+        <v>308.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>318.3734759809475</v>
+        <v>317.3734759809475</v>
       </c>
       <c r="X26" t="n">
-        <v>272.2818334606677</v>
+        <v>271.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>191.3174326828064</v>
+        <v>190.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -2629,25 +2629,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>64.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C27" t="n">
-        <v>41.09991244551929</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>205.4752542749594</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F27" t="n">
-        <v>19.63624233787687</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>4.988856629744324</v>
+        <v>3.988856629744305</v>
       </c>
       <c r="H27" t="n">
-        <v>324.9181060543457</v>
+        <v>3.918106054345685</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,28 +2677,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>500.6658350282283</v>
+        <v>369.2034024054851</v>
       </c>
       <c r="S27" t="n">
-        <v>132.6204622287622</v>
+        <v>131.6204622287622</v>
       </c>
       <c r="T27" t="n">
-        <v>82.33200106657043</v>
+        <v>81.3320010665704</v>
       </c>
       <c r="U27" t="n">
-        <v>80.16097296773391</v>
+        <v>79.16097296773393</v>
       </c>
       <c r="V27" t="n">
-        <v>94.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W27" t="n">
-        <v>112.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>99.86273944538755</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y27" t="n">
-        <v>79.39139276613435</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="28">
@@ -2738,28 +2738,28 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>8.981300288926718</v>
       </c>
       <c r="M28" t="n">
-        <v>97.29942345663355</v>
+        <v>100.9790376320581</v>
       </c>
       <c r="N28" t="n">
-        <v>154.8782392061111</v>
+        <v>153.8782392061111</v>
       </c>
       <c r="O28" t="n">
-        <v>231.4906132593428</v>
+        <v>230.4906132593428</v>
       </c>
       <c r="P28" t="n">
-        <v>291.3315694594251</v>
+        <v>290.3315694594251</v>
       </c>
       <c r="Q28" t="n">
-        <v>353.140266425598</v>
+        <v>352.140266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>378.304521423774</v>
+        <v>377.304521423774</v>
       </c>
       <c r="S28" t="n">
-        <v>31.40572560449478</v>
+        <v>30.40572560449476</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2808,7 +2808,7 @@
         <v>72.64103056282391</v>
       </c>
       <c r="I29" t="n">
-        <v>5.114980330139051</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>5.114980330137827</v>
       </c>
       <c r="S29" t="n">
         <v>141.8769617721721</v>
@@ -2866,16 +2866,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C30" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D30" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>342.6720972219126</v>
+        <v>211.2096645991693</v>
       </c>
       <c r="F30" t="n">
         <v>18.63624233787687</v>
@@ -2887,7 +2887,7 @@
         <v>3.918106054345685</v>
       </c>
       <c r="I30" t="n">
-        <v>191.2806311743674</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2929,10 +2929,10 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W30" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>418.1196756482769</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y30" t="n">
         <v>78.39139276613435</v>
@@ -3042,7 +3042,7 @@
         <v>81.35435721163932</v>
       </c>
       <c r="H32" t="n">
-        <v>77.75601089296302</v>
+        <v>77.7560108929617</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>40.09991244551929</v>
+        <v>229.637479822776</v>
       </c>
       <c r="D33" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
         <v>3.988856629744324</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>369.2034024054851</v>
+        <v>179.6658350282283</v>
       </c>
       <c r="S33" t="n">
         <v>131.6204622287622</v>
@@ -3160,7 +3160,7 @@
         <v>81.33200106657043</v>
       </c>
       <c r="U33" t="n">
-        <v>400.1609729677339</v>
+        <v>79.16097296773391</v>
       </c>
       <c r="V33" t="n">
         <v>93.51066719152016</v>
@@ -3172,7 +3172,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y33" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="34">
@@ -3276,10 +3276,10 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>57.35435721163932</v>
+        <v>57.35435721163935</v>
       </c>
       <c r="H35" t="n">
-        <v>48.6410305628239</v>
+        <v>48.64103056282391</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3318,7 +3318,7 @@
         <v>235.5338832361016</v>
       </c>
       <c r="U35" t="n">
-        <v>304.1090553425805</v>
+        <v>307.5944356727188</v>
       </c>
       <c r="V35" t="n">
         <v>284.8510241668239</v>
@@ -3327,7 +3327,7 @@
         <v>293.3734759809475</v>
       </c>
       <c r="X35" t="n">
-        <v>250.7672137908058</v>
+        <v>247.2818334606677</v>
       </c>
       <c r="Y35" t="n">
         <v>166.3174326828064</v>
@@ -3340,25 +3340,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>384.5565566463266</v>
+        <v>39.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>16.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>2.937686897702633</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>84.37903040628549</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>324.9181060543457</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3394,19 +3394,19 @@
         <v>107.6204622287622</v>
       </c>
       <c r="T36" t="n">
-        <v>57.33200106657042</v>
+        <v>57.3320010665704</v>
       </c>
       <c r="U36" t="n">
-        <v>55.16097296773392</v>
+        <v>161.9498000977611</v>
       </c>
       <c r="V36" t="n">
-        <v>414.5106671915202</v>
+        <v>69.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>87.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>419.8627394453875</v>
+        <v>74.86273944538755</v>
       </c>
       <c r="Y36" t="n">
         <v>54.39139276613435</v>
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>76.97903763205809</v>
+        <v>76.97903763205807</v>
       </c>
       <c r="N37" t="n">
         <v>129.8782392061111</v>
@@ -3470,7 +3470,7 @@
         <v>353.304521423774</v>
       </c>
       <c r="S37" t="n">
-        <v>6.405725604494783</v>
+        <v>6.405725604494762</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3516,7 +3516,7 @@
         <v>57.35435721163932</v>
       </c>
       <c r="H38" t="n">
-        <v>48.6410305628239</v>
+        <v>52.12641089296218</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.485380330137959</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>117.8769617721721</v>
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>384.5565566463266</v>
+        <v>39.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>16.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>2.937686897702633</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>89.7427880684086</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
         <v>500.6658350282283</v>
       </c>
       <c r="S39" t="n">
-        <v>107.6204622287622</v>
+        <v>197.3632502972163</v>
       </c>
       <c r="T39" t="n">
         <v>57.33200106657042</v>
@@ -3643,7 +3643,7 @@
         <v>87.37314290982852</v>
       </c>
       <c r="X39" t="n">
-        <v>419.8627394453875</v>
+        <v>74.86273944538755</v>
       </c>
       <c r="Y39" t="n">
         <v>54.39139276613435</v>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>160.9993129555745</v>
       </c>
       <c r="C41" t="n">
         <v>128.4745782429939</v>
@@ -3744,16 +3744,16 @@
         <v>89.33915573984979</v>
       </c>
       <c r="E41" t="n">
-        <v>83.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>83.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>81.35435721163935</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>72.64103056282391</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3792,7 +3792,7 @@
         <v>259.5338832361016</v>
       </c>
       <c r="U41" t="n">
-        <v>328.1090553425805</v>
+        <v>316.8427417620622</v>
       </c>
       <c r="V41" t="n">
         <v>308.8510241668239</v>
@@ -3801,7 +3801,7 @@
         <v>317.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>99.76652674637987</v>
+        <v>271.2818334606677</v>
       </c>
       <c r="Y41" t="n">
         <v>190.3174326828064</v>
@@ -3817,7 +3817,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D42" t="n">
         <v>26.93768689770263</v>
@@ -3826,13 +3826,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>324.9888566297443</v>
+        <v>3.988856629744305</v>
       </c>
       <c r="H42" t="n">
-        <v>3.918106054345685</v>
+        <v>193.0818342167521</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>77.25571792066825</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>179.6658350282283</v>
@@ -3868,7 +3868,7 @@
         <v>131.6204622287622</v>
       </c>
       <c r="T42" t="n">
-        <v>193.2400113083085</v>
+        <v>81.3320010665704</v>
       </c>
       <c r="U42" t="n">
         <v>79.16097296773393</v>
@@ -3877,7 +3877,7 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>98.86273944538755</v>
@@ -3975,10 +3975,10 @@
         <v>160.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>128.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>89.33915573984979</v>
+        <v>27.17607608515386</v>
       </c>
       <c r="E44" t="n">
         <v>83.36328960686865</v>
@@ -3987,7 +3987,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>20.12157100244479</v>
+        <v>81.35435721163932</v>
       </c>
       <c r="H44" t="n">
         <v>72.6410305628239</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>141.8769617721721</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>259.5338832361016</v>
@@ -4038,7 +4038,7 @@
         <v>317.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>271.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>190.3174326828064</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C45" t="n">
         <v>40.09991244551929</v>
@@ -4060,7 +4060,7 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E45" t="n">
-        <v>210.835825384319</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F45" t="n">
         <v>339.6362423378769</v>
@@ -4069,10 +4069,10 @@
         <v>3.988856629744324</v>
       </c>
       <c r="H45" t="n">
-        <v>3.918106054345659</v>
+        <v>245.5454851217162</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>191.2806311743674</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,10 +4096,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.205979399150237e-11</v>
+        <v>77.25571792066825</v>
       </c>
       <c r="R45" t="n">
-        <v>179.6658350282283</v>
+        <v>500.6658350282283</v>
       </c>
       <c r="S45" t="n">
         <v>131.6204622287622</v>
@@ -4120,7 +4120,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="46">
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108.9522717631734</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C2" t="n">
-        <v>58.97795030560376</v>
+        <v>56.89417848844987</v>
       </c>
       <c r="D2" t="n">
-        <v>48.53435864918983</v>
+        <v>46.45058683203594</v>
       </c>
       <c r="E2" t="n">
-        <v>44.12699540992857</v>
+        <v>42.04322359277468</v>
       </c>
       <c r="F2" t="n">
-        <v>39.1879765129469</v>
+        <v>37.10420469579301</v>
       </c>
       <c r="G2" t="n">
-        <v>33.68554531243061</v>
+        <v>33.72713203391683</v>
       </c>
       <c r="H2" t="n">
         <v>29.92</v>
@@ -4321,22 +4321,22 @@
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>400.18</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K2" t="n">
-        <v>770.4399999999999</v>
+        <v>82.16427879223495</v>
       </c>
       <c r="L2" t="n">
-        <v>835.7580309547739</v>
+        <v>326.5557936111288</v>
       </c>
       <c r="M2" t="n">
-        <v>835.7580309547739</v>
+        <v>696.8157936111288</v>
       </c>
       <c r="N2" t="n">
-        <v>835.7580309547739</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O2" t="n">
-        <v>835.9517423879801</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P2" t="n">
         <v>1125.74</v>
@@ -4345,28 +4345,28 @@
         <v>1496</v>
       </c>
       <c r="R2" t="n">
-        <v>1496</v>
+        <v>1494.026862160815</v>
       </c>
       <c r="S2" t="n">
-        <v>1409.817240786446</v>
+        <v>1407.751569573321</v>
       </c>
       <c r="T2" t="n">
-        <v>1223.104724853325</v>
+        <v>1221.021277892776</v>
       </c>
       <c r="U2" t="n">
-        <v>971.3998265579412</v>
+        <v>969.3160547407859</v>
       </c>
       <c r="V2" t="n">
-        <v>739.2270748742807</v>
+        <v>737.1433030571254</v>
       </c>
       <c r="W2" t="n">
-        <v>498.4457860046367</v>
+        <v>496.3620141874814</v>
       </c>
       <c r="X2" t="n">
-        <v>304.221711801942</v>
+        <v>302.1379399847867</v>
       </c>
       <c r="Y2" t="n">
-        <v>191.779860607188</v>
+        <v>189.6960887900328</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1038.198352868651</v>
+        <v>939.3202578862974</v>
       </c>
       <c r="C3" t="n">
-        <v>1038.198352868651</v>
+        <v>939.3202578862974</v>
       </c>
       <c r="D3" t="n">
-        <v>1038.198352868651</v>
+        <v>587.8680488987191</v>
       </c>
       <c r="E3" t="n">
-        <v>692.064921331366</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="F3" t="n">
-        <v>692.064921331366</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="G3" t="n">
-        <v>363.2610448042753</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="H3" t="n">
-        <v>29.92</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="I3" t="n">
-        <v>29.92</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="J3" t="n">
-        <v>174.7997405526575</v>
+        <v>174.7984703728012</v>
       </c>
       <c r="K3" t="n">
-        <v>399.7536728734559</v>
+        <v>399.4085458068072</v>
       </c>
       <c r="L3" t="n">
-        <v>719.1893684309202</v>
+        <v>718.3818833454036</v>
       </c>
       <c r="M3" t="n">
-        <v>858.5689698052438</v>
+        <v>860.0360750882628</v>
       </c>
       <c r="N3" t="n">
-        <v>1049.447603846774</v>
+        <v>1050.360878846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1341.181292511625</v>
+        <v>1341.587921002191</v>
       </c>
       <c r="P3" t="n">
         <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1350.015760438433</v>
+        <v>1349.738421006376</v>
       </c>
       <c r="R3" t="n">
-        <v>1215.283546668734</v>
+        <v>1074.528305302336</v>
       </c>
       <c r="S3" t="n">
-        <v>1152.244248057634</v>
+        <v>1011.448650297106</v>
       </c>
       <c r="T3" t="n">
-        <v>1147.743132057478</v>
+        <v>1006.938776911777</v>
       </c>
       <c r="U3" t="n">
-        <v>1147.545513088736</v>
+        <v>1006.741015004213</v>
       </c>
       <c r="V3" t="n">
-        <v>1132.888273501341</v>
+        <v>992.0837754168188</v>
       </c>
       <c r="W3" t="n">
-        <v>1100.188129147979</v>
+        <v>959.3836310634566</v>
       </c>
       <c r="X3" t="n">
-        <v>1080.12475597082</v>
+        <v>939.3202578862974</v>
       </c>
       <c r="Y3" t="n">
-        <v>1038.198352868651</v>
+        <v>939.3202578862974</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>214.9770609416759</v>
+        <v>216.7976894066533</v>
       </c>
       <c r="C4" t="n">
-        <v>340.9790667601117</v>
+        <v>342.7996952250891</v>
       </c>
       <c r="D4" t="n">
-        <v>454.2982108851118</v>
+        <v>456.1188393500892</v>
       </c>
       <c r="E4" t="n">
-        <v>572.1271150965248</v>
+        <v>573.9477435615022</v>
       </c>
       <c r="F4" t="n">
-        <v>696.4880876884603</v>
+        <v>698.3087161534377</v>
       </c>
       <c r="G4" t="n">
-        <v>850.080319149116</v>
+        <v>851.8991623681918</v>
       </c>
       <c r="H4" t="n">
-        <v>1021.247640046219</v>
+        <v>1023.050610806278</v>
       </c>
       <c r="I4" t="n">
-        <v>1247.963989146236</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="J4" t="n">
-        <v>1247.963989146236</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K4" t="n">
-        <v>1379.89938701753</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L4" t="n">
-        <v>1384.190642354444</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M4" t="n">
-        <v>1292.035379967367</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N4" t="n">
-        <v>1148.109935496879</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O4" t="n">
-        <v>932.0114521582484</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P4" t="n">
-        <v>664.5713836531163</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q4" t="n">
-        <v>351.3034377686739</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R4" t="n">
         <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>29.92</v>
+        <v>70.37478771712394</v>
       </c>
       <c r="T4" t="n">
-        <v>29.92</v>
+        <v>105.0403517403612</v>
       </c>
       <c r="U4" t="n">
-        <v>29.92</v>
+        <v>105.0403517403612</v>
       </c>
       <c r="V4" t="n">
-        <v>29.92</v>
+        <v>105.0403517403612</v>
       </c>
       <c r="W4" t="n">
-        <v>29.92</v>
+        <v>105.0403517403612</v>
       </c>
       <c r="X4" t="n">
-        <v>103.2197232753838</v>
+        <v>105.0403517403612</v>
       </c>
       <c r="Y4" t="n">
-        <v>103.2197232753838</v>
+        <v>105.0403517403612</v>
       </c>
     </row>
     <row r="5">
@@ -4534,76 +4534,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106.822852516955</v>
+        <v>108.9522717631734</v>
       </c>
       <c r="C5" t="n">
-        <v>56.84853105938534</v>
+        <v>58.97795030560376</v>
       </c>
       <c r="D5" t="n">
-        <v>46.40493940297141</v>
+        <v>48.53435864918983</v>
       </c>
       <c r="E5" t="n">
-        <v>41.99757616371015</v>
+        <v>44.12699540992857</v>
       </c>
       <c r="F5" t="n">
-        <v>37.05855726672848</v>
+        <v>39.1879765129469</v>
       </c>
       <c r="G5" t="n">
-        <v>33.6855453124306</v>
+        <v>35.81496455864902</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92</v>
+        <v>32.04941924621842</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>30.35747929474751</v>
+        <v>400.18</v>
       </c>
       <c r="K5" t="n">
-        <v>400.6174792947475</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>465.9355102495214</v>
+        <v>1140.7</v>
       </c>
       <c r="M5" t="n">
-        <v>696.2434790885159</v>
+        <v>1140.7</v>
       </c>
       <c r="N5" t="n">
-        <v>696.2434790885159</v>
+        <v>1140.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1066.503479088516</v>
+        <v>1140.893711433206</v>
       </c>
       <c r="P5" t="n">
-        <v>1125.74</v>
+        <v>1200.130232344691</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
       </c>
       <c r="R5" t="n">
-        <v>1493.870580753781</v>
+        <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1407.687821540228</v>
+        <v>1409.817240786446</v>
       </c>
       <c r="T5" t="n">
-        <v>1220.975305607106</v>
+        <v>1223.104724853325</v>
       </c>
       <c r="U5" t="n">
-        <v>969.2704073117228</v>
+        <v>971.3998265579412</v>
       </c>
       <c r="V5" t="n">
-        <v>737.0976556280623</v>
+        <v>739.2270748742807</v>
       </c>
       <c r="W5" t="n">
-        <v>496.3163667584182</v>
+        <v>498.4457860046367</v>
       </c>
       <c r="X5" t="n">
-        <v>302.0922925557235</v>
+        <v>304.221711801942</v>
       </c>
       <c r="Y5" t="n">
-        <v>189.6504413609696</v>
+        <v>191.779860607188</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1226.108995532387</v>
+        <v>394.6673863086054</v>
       </c>
       <c r="C6" t="n">
-        <v>1226.108995532387</v>
+        <v>29.92</v>
       </c>
       <c r="D6" t="n">
-        <v>874.6567865448089</v>
+        <v>29.92</v>
       </c>
       <c r="E6" t="n">
-        <v>584.5268095320936</v>
+        <v>29.92</v>
       </c>
       <c r="F6" t="n">
-        <v>241.4598980796927</v>
+        <v>29.92</v>
       </c>
       <c r="G6" t="n">
-        <v>241.4598980796927</v>
+        <v>29.92</v>
       </c>
       <c r="H6" t="n">
-        <v>241.4598980796927</v>
+        <v>29.92</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
@@ -4658,31 +4658,31 @@
         <v>1496</v>
       </c>
       <c r="Q6" t="n">
-        <v>1496</v>
+        <v>1350.015760438433</v>
       </c>
       <c r="R6" t="n">
-        <v>1361.267786230301</v>
+        <v>1215.283546668734</v>
       </c>
       <c r="S6" t="n">
-        <v>1298.228487619202</v>
+        <v>1152.244248057635</v>
       </c>
       <c r="T6" t="n">
-        <v>1293.727371619045</v>
+        <v>1147.743132057478</v>
       </c>
       <c r="U6" t="n">
-        <v>1293.529752650303</v>
+        <v>1147.545513088736</v>
       </c>
       <c r="V6" t="n">
-        <v>1278.872513062909</v>
+        <v>1132.888273501342</v>
       </c>
       <c r="W6" t="n">
-        <v>1246.172368709546</v>
+        <v>1100.188129147979</v>
       </c>
       <c r="X6" t="n">
-        <v>1226.108995532387</v>
+        <v>722.4103513702016</v>
       </c>
       <c r="Y6" t="n">
-        <v>1226.108995532387</v>
+        <v>394.6673863086054</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>573.6288079129881</v>
+        <v>1021.391060366543</v>
       </c>
       <c r="C7" t="n">
-        <v>699.6308137314239</v>
+        <v>1147.393066184978</v>
       </c>
       <c r="D7" t="n">
-        <v>812.949957856424</v>
+        <v>1260.712210309978</v>
       </c>
       <c r="E7" t="n">
-        <v>930.7788620678371</v>
+        <v>1378.541114521391</v>
       </c>
       <c r="F7" t="n">
-        <v>1055.139834659773</v>
+        <v>1384.190642354444</v>
       </c>
       <c r="G7" t="n">
-        <v>1208.732066120428</v>
+        <v>1384.190642354444</v>
       </c>
       <c r="H7" t="n">
-        <v>1379.899387017531</v>
+        <v>1384.190642354444</v>
       </c>
       <c r="I7" t="n">
-        <v>1379.899387017531</v>
+        <v>1384.190642354444</v>
       </c>
       <c r="J7" t="n">
-        <v>1379.899387017531</v>
+        <v>1384.190642354444</v>
       </c>
       <c r="K7" t="n">
-        <v>1379.899387017531</v>
+        <v>1384.190642354444</v>
       </c>
       <c r="L7" t="n">
         <v>1384.190642354444</v>
@@ -4743,25 +4743,25 @@
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>70.40589968433704</v>
+        <v>29.92</v>
       </c>
       <c r="T7" t="n">
-        <v>70.40589968433704</v>
+        <v>29.92</v>
       </c>
       <c r="U7" t="n">
-        <v>70.40589968433704</v>
+        <v>276.4813198514014</v>
       </c>
       <c r="V7" t="n">
-        <v>269.227292570283</v>
+        <v>475.3027127373473</v>
       </c>
       <c r="W7" t="n">
-        <v>441.1182108299604</v>
+        <v>647.1936309970248</v>
       </c>
       <c r="X7" t="n">
-        <v>462.2195072339559</v>
+        <v>798.2244220212183</v>
       </c>
       <c r="Y7" t="n">
-        <v>573.6288079129881</v>
+        <v>909.6337227002506</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106.822852516955</v>
+        <v>108.9522717631734</v>
       </c>
       <c r="C8" t="n">
-        <v>56.84853105938534</v>
+        <v>58.97795030560376</v>
       </c>
       <c r="D8" t="n">
-        <v>46.40493940297141</v>
+        <v>48.53435864918983</v>
       </c>
       <c r="E8" t="n">
-        <v>41.99757616371015</v>
+        <v>44.12699540992857</v>
       </c>
       <c r="F8" t="n">
-        <v>37.05855726672848</v>
+        <v>39.1879765129469</v>
       </c>
       <c r="G8" t="n">
-        <v>33.6855453124306</v>
+        <v>35.81496455864902</v>
       </c>
       <c r="H8" t="n">
         <v>29.92</v>
@@ -4795,16 +4795,16 @@
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>400.18</v>
+        <v>30.35747929474751</v>
       </c>
       <c r="K8" t="n">
-        <v>770.4399999999999</v>
+        <v>400.6174792947475</v>
       </c>
       <c r="L8" t="n">
-        <v>1140.7</v>
+        <v>770.8774792947474</v>
       </c>
       <c r="M8" t="n">
-        <v>1140.7</v>
+        <v>1066.30976765531</v>
       </c>
       <c r="N8" t="n">
         <v>1436.56976765531</v>
@@ -4831,16 +4831,16 @@
         <v>971.3998265579412</v>
       </c>
       <c r="V8" t="n">
-        <v>737.0976556280623</v>
+        <v>739.2270748742807</v>
       </c>
       <c r="W8" t="n">
-        <v>496.3163667584182</v>
+        <v>498.4457860046367</v>
       </c>
       <c r="X8" t="n">
-        <v>302.0922925557235</v>
+        <v>304.221711801942</v>
       </c>
       <c r="Y8" t="n">
-        <v>189.6504413609696</v>
+        <v>191.779860607188</v>
       </c>
     </row>
     <row r="9">
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1053.24299696707</v>
+        <v>381.3722089875785</v>
       </c>
       <c r="C9" t="n">
-        <v>1053.24299696707</v>
+        <v>381.3722089875785</v>
       </c>
       <c r="D9" t="n">
-        <v>701.7907879794916</v>
+        <v>29.92</v>
       </c>
       <c r="E9" t="n">
-        <v>701.7907879794916</v>
+        <v>29.92</v>
       </c>
       <c r="F9" t="n">
-        <v>358.7238765270907</v>
+        <v>29.92</v>
       </c>
       <c r="G9" t="n">
         <v>29.92</v>
@@ -4883,10 +4883,10 @@
         <v>719.1893684309202</v>
       </c>
       <c r="M9" t="n">
-        <v>858.5689698052438</v>
+        <v>861.3831101737794</v>
       </c>
       <c r="N9" t="n">
-        <v>1049.447603846774</v>
+        <v>1052.26174421531</v>
       </c>
       <c r="O9" t="n">
         <v>1341.181292511625</v>
@@ -4895,31 +4895,31 @@
         <v>1496</v>
       </c>
       <c r="Q9" t="n">
-        <v>1496</v>
+        <v>1350.015760438433</v>
       </c>
       <c r="R9" t="n">
-        <v>1188.401787664984</v>
+        <v>972.2379826606552</v>
       </c>
       <c r="S9" t="n">
-        <v>1125.362489053884</v>
+        <v>909.1986840495556</v>
       </c>
       <c r="T9" t="n">
-        <v>1120.861373053727</v>
+        <v>904.6975680493987</v>
       </c>
       <c r="U9" t="n">
-        <v>1120.663754084985</v>
+        <v>904.4999490806566</v>
       </c>
       <c r="V9" t="n">
-        <v>1106.006514497591</v>
+        <v>526.7221713028788</v>
       </c>
       <c r="W9" t="n">
-        <v>1073.306370144229</v>
+        <v>494.0220269495167</v>
       </c>
       <c r="X9" t="n">
-        <v>1053.24299696707</v>
+        <v>381.3722089875785</v>
       </c>
       <c r="Y9" t="n">
-        <v>1053.24299696707</v>
+        <v>381.3722089875785</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>633.4723065733156</v>
+        <v>572.127115096525</v>
       </c>
       <c r="C10" t="n">
-        <v>759.4743123917514</v>
+        <v>572.127115096525</v>
       </c>
       <c r="D10" t="n">
-        <v>872.7934565167515</v>
+        <v>572.127115096525</v>
       </c>
       <c r="E10" t="n">
-        <v>990.6223607281645</v>
+        <v>572.127115096525</v>
       </c>
       <c r="F10" t="n">
-        <v>1081.087923586047</v>
+        <v>696.4880876884605</v>
       </c>
       <c r="G10" t="n">
-        <v>1081.087923586047</v>
+        <v>850.0803191491162</v>
       </c>
       <c r="H10" t="n">
-        <v>1252.255244483149</v>
+        <v>1021.247640046219</v>
       </c>
       <c r="I10" t="n">
-        <v>1252.255244483149</v>
+        <v>1247.963989146236</v>
       </c>
       <c r="J10" t="n">
-        <v>1252.255244483149</v>
+        <v>1247.963989146236</v>
       </c>
       <c r="K10" t="n">
-        <v>1384.190642354444</v>
+        <v>1379.899387017531</v>
       </c>
       <c r="L10" t="n">
         <v>1384.190642354444</v>
@@ -4986,19 +4986,19 @@
         <v>259.2748772037976</v>
       </c>
       <c r="U10" t="n">
-        <v>259.2748772037976</v>
+        <v>505.836197055199</v>
       </c>
       <c r="V10" t="n">
-        <v>259.2748772037976</v>
+        <v>572.127115096525</v>
       </c>
       <c r="W10" t="n">
-        <v>259.2748772037976</v>
+        <v>572.127115096525</v>
       </c>
       <c r="X10" t="n">
-        <v>410.3056682279912</v>
+        <v>572.127115096525</v>
       </c>
       <c r="Y10" t="n">
-        <v>521.7149689070235</v>
+        <v>572.127115096525</v>
       </c>
     </row>
     <row r="11">
@@ -5008,16 +5008,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>596.4271111840278</v>
+        <v>596.4271111840277</v>
       </c>
       <c r="C11" t="n">
-        <v>466.6548099284784</v>
+        <v>466.6548099284783</v>
       </c>
       <c r="D11" t="n">
         <v>376.4132384740846</v>
       </c>
       <c r="E11" t="n">
-        <v>292.2078954368436</v>
+        <v>292.2078954368435</v>
       </c>
       <c r="F11" t="n">
         <v>207.4708967418821</v>
@@ -5035,22 +5035,22 @@
         <v>561.1174722838869</v>
       </c>
       <c r="K11" t="n">
-        <v>1203.627472283887</v>
+        <v>737.8015633894146</v>
       </c>
       <c r="L11" t="n">
-        <v>1846.137472283887</v>
+        <v>956.9938018818768</v>
       </c>
       <c r="M11" t="n">
-        <v>2232.063478208073</v>
+        <v>1000.959637376511</v>
       </c>
       <c r="N11" t="n">
-        <v>2232.063478208073</v>
+        <v>1643.469637376511</v>
       </c>
       <c r="O11" t="n">
-        <v>2396.546421048315</v>
+        <v>1807.952580216753</v>
       </c>
       <c r="P11" t="n">
-        <v>2596</v>
+        <v>2007.406159168438</v>
       </c>
       <c r="Q11" t="n">
         <v>2596</v>
@@ -5077,7 +5077,7 @@
         <v>951.292510818756</v>
       </c>
       <c r="Y11" t="n">
-        <v>759.0526798260223</v>
+        <v>759.0526798260222</v>
       </c>
     </row>
     <row r="12">
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>684.0315848124831</v>
+        <v>816.8219207950519</v>
       </c>
       <c r="C12" t="n">
-        <v>643.526622746302</v>
+        <v>452.0745344864466</v>
       </c>
       <c r="D12" t="n">
-        <v>424.8647497412924</v>
+        <v>100.6223254988682</v>
       </c>
       <c r="E12" t="n">
-        <v>402.9737424464312</v>
+        <v>78.73131820400693</v>
       </c>
       <c r="F12" t="n">
-        <v>384.1492552364546</v>
+        <v>59.90683099403029</v>
       </c>
       <c r="G12" t="n">
-        <v>55.87768288317746</v>
+        <v>55.87768288317744</v>
       </c>
       <c r="H12" t="n">
         <v>51.92</v>
@@ -5144,19 +5144,19 @@
         <v>1862.673475647767</v>
       </c>
       <c r="U12" t="n">
-        <v>1458.470472650056</v>
+        <v>1782.71289689248</v>
       </c>
       <c r="V12" t="n">
-        <v>1364.015253264682</v>
+        <v>1688.257677507106</v>
       </c>
       <c r="W12" t="n">
-        <v>1251.51712911334</v>
+        <v>1575.759553355764</v>
       </c>
       <c r="X12" t="n">
-        <v>1151.655776138201</v>
+        <v>1284.44611212077</v>
       </c>
       <c r="Y12" t="n">
-        <v>1072.472551121904</v>
+        <v>1205.262887104473</v>
       </c>
     </row>
     <row r="13">
@@ -5181,7 +5181,7 @@
         <v>855.3537498786892</v>
       </c>
       <c r="G13" t="n">
-        <v>922.0615630138847</v>
+        <v>931.1733665852466</v>
       </c>
       <c r="H13" t="n">
         <v>1018.907636370004</v>
@@ -5211,16 +5211,16 @@
         <v>819.445771165522</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.7485323517866</v>
+        <v>463.7485323517867</v>
       </c>
       <c r="R13" t="n">
-        <v>82.63285414595431</v>
+        <v>82.63285414595433</v>
       </c>
       <c r="S13" t="n">
         <v>51.92</v>
       </c>
       <c r="T13" t="n">
-        <v>164.447805388313</v>
+        <v>164.4478053883131</v>
       </c>
       <c r="U13" t="n">
         <v>332.8229826167636</v>
@@ -5260,7 +5260,7 @@
         <v>208.717543540001</v>
       </c>
       <c r="G14" t="n">
-        <v>125.2947783462868</v>
+        <v>126.5414251444057</v>
       </c>
       <c r="H14" t="n">
         <v>51.92</v>
@@ -5272,22 +5272,22 @@
         <v>135.1157830635917</v>
       </c>
       <c r="K14" t="n">
-        <v>311.7998741691194</v>
+        <v>777.6257830635917</v>
       </c>
       <c r="L14" t="n">
-        <v>954.3098741691193</v>
+        <v>996.818021556054</v>
       </c>
       <c r="M14" t="n">
-        <v>1596.819874169119</v>
+        <v>1000.959637376511</v>
       </c>
       <c r="N14" t="n">
-        <v>1596.819874169119</v>
+        <v>1643.469637376511</v>
       </c>
       <c r="O14" t="n">
-        <v>1953.49</v>
+        <v>1807.952580216753</v>
       </c>
       <c r="P14" t="n">
-        <v>2596</v>
+        <v>2007.406159168438</v>
       </c>
       <c r="Q14" t="n">
         <v>2596</v>
@@ -5324,16 +5324,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1141.064345037476</v>
+        <v>492.5794965526277</v>
       </c>
       <c r="C15" t="n">
-        <v>776.316958728871</v>
+        <v>127.8321102440223</v>
       </c>
       <c r="D15" t="n">
-        <v>424.8647497412925</v>
+        <v>100.6223254988682</v>
       </c>
       <c r="E15" t="n">
-        <v>402.9737424464312</v>
+        <v>78.73131820400693</v>
       </c>
       <c r="F15" t="n">
         <v>59.9068309940303</v>
@@ -5393,7 +5393,7 @@
         <v>1284.44611212077</v>
       </c>
       <c r="Y15" t="n">
-        <v>1205.262887104473</v>
+        <v>881.0204628620486</v>
       </c>
     </row>
     <row r="16">
@@ -5403,25 +5403,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>677.570919560543</v>
+        <v>686.6827231319049</v>
       </c>
       <c r="C16" t="n">
-        <v>725.3629253789787</v>
+        <v>734.4747289503407</v>
       </c>
       <c r="D16" t="n">
-        <v>760.4720695039788</v>
+        <v>769.5838730753408</v>
       </c>
       <c r="E16" t="n">
-        <v>800.0909737153918</v>
+        <v>809.2027772867538</v>
       </c>
       <c r="F16" t="n">
-        <v>846.2419463073272</v>
+        <v>855.3537498786892</v>
       </c>
       <c r="G16" t="n">
-        <v>922.0615630138847</v>
+        <v>931.1733665852466</v>
       </c>
       <c r="H16" t="n">
-        <v>1018.907636370004</v>
+        <v>1028.019439941366</v>
       </c>
       <c r="I16" t="n">
         <v>1180.567352683136</v>
@@ -5457,22 +5457,22 @@
         <v>51.92</v>
       </c>
       <c r="T16" t="n">
-        <v>155.336001816951</v>
+        <v>164.447805388313</v>
       </c>
       <c r="U16" t="n">
-        <v>323.7111790454016</v>
+        <v>332.8229826167636</v>
       </c>
       <c r="V16" t="n">
-        <v>444.3225719313476</v>
+        <v>453.4343755027096</v>
       </c>
       <c r="W16" t="n">
-        <v>538.003490191025</v>
+        <v>547.115293762387</v>
       </c>
       <c r="X16" t="n">
-        <v>610.8242812152185</v>
+        <v>619.9360847865805</v>
       </c>
       <c r="Y16" t="n">
-        <v>644.0235818942508</v>
+        <v>653.1353854656128</v>
       </c>
     </row>
     <row r="17">
@@ -5482,25 +5482,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>596.4271111840278</v>
+        <v>597.6737579821468</v>
       </c>
       <c r="C17" t="n">
-        <v>466.6548099284784</v>
+        <v>467.9014567265973</v>
       </c>
       <c r="D17" t="n">
-        <v>376.4132384740846</v>
+        <v>377.6598852722036</v>
       </c>
       <c r="E17" t="n">
-        <v>292.2078954368436</v>
+        <v>293.4545422349625</v>
       </c>
       <c r="F17" t="n">
-        <v>207.4708967418821</v>
+        <v>208.717543540001</v>
       </c>
       <c r="G17" t="n">
-        <v>125.2947783462868</v>
+        <v>126.5414251444057</v>
       </c>
       <c r="H17" t="n">
-        <v>51.92</v>
+        <v>53.16664679811893</v>
       </c>
       <c r="I17" t="n">
         <v>51.92</v>
@@ -5509,49 +5509,49 @@
         <v>561.1174722838869</v>
       </c>
       <c r="K17" t="n">
-        <v>1203.627472283887</v>
+        <v>737.8015633894146</v>
       </c>
       <c r="L17" t="n">
-        <v>1846.137472283887</v>
+        <v>1380.311563389415</v>
       </c>
       <c r="M17" t="n">
-        <v>1846.137472283887</v>
+        <v>1589.553478208073</v>
       </c>
       <c r="N17" t="n">
-        <v>1846.137472283887</v>
+        <v>2232.063478208073</v>
       </c>
       <c r="O17" t="n">
-        <v>2010.620415124128</v>
+        <v>2396.546421048315</v>
       </c>
       <c r="P17" t="n">
-        <v>2210.073994075814</v>
+        <v>2596</v>
       </c>
       <c r="Q17" t="n">
         <v>2596</v>
       </c>
       <c r="R17" t="n">
-        <v>2594.753353201881</v>
+        <v>2596</v>
       </c>
       <c r="S17" t="n">
-        <v>2451.443290805747</v>
+        <v>2452.689937603866</v>
       </c>
       <c r="T17" t="n">
-        <v>2189.287853193523</v>
+        <v>2190.534499991642</v>
       </c>
       <c r="U17" t="n">
-        <v>1857.864564968695</v>
+        <v>1859.111211766814</v>
       </c>
       <c r="V17" t="n">
-        <v>1545.893833487054</v>
+        <v>1547.140480285173</v>
       </c>
       <c r="W17" t="n">
-        <v>1225.31456481943</v>
+        <v>1226.561211617549</v>
       </c>
       <c r="X17" t="n">
-        <v>951.292510818756</v>
+        <v>952.5391576168749</v>
       </c>
       <c r="Y17" t="n">
-        <v>759.0526798260223</v>
+        <v>760.2993266241413</v>
       </c>
     </row>
     <row r="18">
@@ -5561,16 +5561,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>359.7891605700588</v>
+        <v>168.3370723102034</v>
       </c>
       <c r="C18" t="n">
-        <v>319.2841985038776</v>
+        <v>127.8321102440223</v>
       </c>
       <c r="D18" t="n">
-        <v>292.0744137587234</v>
+        <v>100.6223254988682</v>
       </c>
       <c r="E18" t="n">
-        <v>270.1834064638622</v>
+        <v>78.73131820400693</v>
       </c>
       <c r="F18" t="n">
         <v>59.9068309940303</v>
@@ -5624,13 +5624,13 @@
         <v>1688.257677507106</v>
       </c>
       <c r="W18" t="n">
-        <v>1575.759553355764</v>
+        <v>1384.307465095909</v>
       </c>
       <c r="X18" t="n">
-        <v>1151.655776138201</v>
+        <v>960.2036878783459</v>
       </c>
       <c r="Y18" t="n">
-        <v>748.2301268794796</v>
+        <v>556.7780386196243</v>
       </c>
     </row>
     <row r="19">
@@ -5640,28 +5640,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>686.6827231319049</v>
+        <v>677.570919560543</v>
       </c>
       <c r="C19" t="n">
-        <v>734.4747289503407</v>
+        <v>725.3629253789787</v>
       </c>
       <c r="D19" t="n">
-        <v>769.5838730753408</v>
+        <v>760.4720695039788</v>
       </c>
       <c r="E19" t="n">
-        <v>809.2027772867538</v>
+        <v>800.0909737153918</v>
       </c>
       <c r="F19" t="n">
-        <v>855.3537498786892</v>
+        <v>846.2419463073272</v>
       </c>
       <c r="G19" t="n">
-        <v>931.1733665852466</v>
+        <v>922.0615630138847</v>
       </c>
       <c r="H19" t="n">
-        <v>1028.019439941366</v>
+        <v>1018.907636370004</v>
       </c>
       <c r="I19" t="n">
-        <v>1189.679156254498</v>
+        <v>1180.567352683136</v>
       </c>
       <c r="J19" t="n">
         <v>1507.490786286407</v>
@@ -5697,19 +5697,19 @@
         <v>164.447805388313</v>
       </c>
       <c r="U19" t="n">
-        <v>332.8229826167636</v>
+        <v>323.7111790454016</v>
       </c>
       <c r="V19" t="n">
-        <v>453.4343755027096</v>
+        <v>444.3225719313476</v>
       </c>
       <c r="W19" t="n">
-        <v>547.115293762387</v>
+        <v>538.003490191025</v>
       </c>
       <c r="X19" t="n">
-        <v>619.9360847865805</v>
+        <v>610.8242812152185</v>
       </c>
       <c r="Y19" t="n">
-        <v>653.1353854656128</v>
+        <v>644.0235818942508</v>
       </c>
     </row>
     <row r="20">
@@ -5719,16 +5719,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>596.4271111840278</v>
+        <v>596.4271111840277</v>
       </c>
       <c r="C20" t="n">
-        <v>466.6548099284784</v>
+        <v>466.6548099284783</v>
       </c>
       <c r="D20" t="n">
         <v>376.4132384740846</v>
       </c>
       <c r="E20" t="n">
-        <v>292.2078954368436</v>
+        <v>292.2078954368435</v>
       </c>
       <c r="F20" t="n">
         <v>207.4708967418821</v>
@@ -5743,25 +5743,25 @@
         <v>51.92</v>
       </c>
       <c r="J20" t="n">
-        <v>561.1174722838869</v>
+        <v>135.1157830635917</v>
       </c>
       <c r="K20" t="n">
-        <v>737.8015633894146</v>
+        <v>311.7998741691194</v>
       </c>
       <c r="L20" t="n">
-        <v>956.9938018818768</v>
+        <v>530.9921126615817</v>
       </c>
       <c r="M20" t="n">
-        <v>1599.503801881877</v>
+        <v>1173.502112661582</v>
       </c>
       <c r="N20" t="n">
-        <v>1643.469637376511</v>
+        <v>1754.036421048315</v>
       </c>
       <c r="O20" t="n">
-        <v>1807.952580216753</v>
+        <v>2396.546421048315</v>
       </c>
       <c r="P20" t="n">
-        <v>2007.406159168438</v>
+        <v>2596</v>
       </c>
       <c r="Q20" t="n">
         <v>2596</v>
@@ -5788,7 +5788,7 @@
         <v>951.292510818756</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.0526798260223</v>
+        <v>759.0526798260222</v>
       </c>
     </row>
     <row r="21">
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>684.0315848124831</v>
+        <v>168.3370723102034</v>
       </c>
       <c r="C21" t="n">
-        <v>643.526622746302</v>
+        <v>127.8321102440223</v>
       </c>
       <c r="D21" t="n">
-        <v>616.3168380011479</v>
+        <v>100.6223254988682</v>
       </c>
       <c r="E21" t="n">
-        <v>270.1834064638624</v>
+        <v>78.73131820400693</v>
       </c>
       <c r="F21" t="n">
-        <v>251.3589192538857</v>
+        <v>59.90683099403029</v>
       </c>
       <c r="G21" t="n">
-        <v>247.3297711430329</v>
+        <v>55.87768288317744</v>
       </c>
       <c r="H21" t="n">
         <v>51.92</v>
@@ -5858,16 +5858,16 @@
         <v>1782.71289689248</v>
       </c>
       <c r="V21" t="n">
-        <v>1364.015253264682</v>
+        <v>1688.257677507106</v>
       </c>
       <c r="W21" t="n">
-        <v>1251.51712911334</v>
+        <v>1384.307465095909</v>
       </c>
       <c r="X21" t="n">
-        <v>1151.655776138201</v>
+        <v>960.2036878783459</v>
       </c>
       <c r="Y21" t="n">
-        <v>1072.472551121904</v>
+        <v>556.7780386196243</v>
       </c>
     </row>
     <row r="22">
@@ -5877,28 +5877,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>677.570919560543</v>
+        <v>686.6827231319049</v>
       </c>
       <c r="C22" t="n">
-        <v>725.3629253789787</v>
+        <v>734.4747289503407</v>
       </c>
       <c r="D22" t="n">
-        <v>760.4720695039788</v>
+        <v>769.5838730753408</v>
       </c>
       <c r="E22" t="n">
-        <v>800.0909737153918</v>
+        <v>809.2027772867538</v>
       </c>
       <c r="F22" t="n">
-        <v>846.2419463073272</v>
+        <v>855.3537498786892</v>
       </c>
       <c r="G22" t="n">
-        <v>922.0615630138847</v>
+        <v>931.1733665852466</v>
       </c>
       <c r="H22" t="n">
-        <v>1018.907636370004</v>
+        <v>1028.019439941366</v>
       </c>
       <c r="I22" t="n">
-        <v>1180.567352683136</v>
+        <v>1189.679156254498</v>
       </c>
       <c r="J22" t="n">
         <v>1507.490786286407</v>
@@ -5922,16 +5922,16 @@
         <v>819.445771165522</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.7485323517866</v>
+        <v>463.7485323517867</v>
       </c>
       <c r="R22" t="n">
-        <v>82.63285414595431</v>
+        <v>82.63285414595433</v>
       </c>
       <c r="S22" t="n">
         <v>51.92</v>
       </c>
       <c r="T22" t="n">
-        <v>164.447805388313</v>
+        <v>164.4478053883131</v>
       </c>
       <c r="U22" t="n">
         <v>332.8229826167636</v>
@@ -5943,10 +5943,10 @@
         <v>547.115293762387</v>
       </c>
       <c r="X22" t="n">
-        <v>610.8242812152185</v>
+        <v>619.9360847865805</v>
       </c>
       <c r="Y22" t="n">
-        <v>644.0235818942508</v>
+        <v>653.1353854656128</v>
       </c>
     </row>
     <row r="23">
@@ -5986,19 +5986,19 @@
         <v>737.8015633894146</v>
       </c>
       <c r="L23" t="n">
-        <v>1380.311563389415</v>
+        <v>956.9938018818768</v>
       </c>
       <c r="M23" t="n">
-        <v>1380.311563389415</v>
+        <v>1146.497057159758</v>
       </c>
       <c r="N23" t="n">
-        <v>1380.311563389415</v>
+        <v>1789.007057159758</v>
       </c>
       <c r="O23" t="n">
-        <v>1544.794506229656</v>
+        <v>1953.49</v>
       </c>
       <c r="P23" t="n">
-        <v>2007.406159168438</v>
+        <v>2596</v>
       </c>
       <c r="Q23" t="n">
         <v>2596</v>
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>684.0315848124831</v>
+        <v>1332.516433297332</v>
       </c>
       <c r="C24" t="n">
-        <v>643.526622746302</v>
+        <v>1100.559382971295</v>
       </c>
       <c r="D24" t="n">
-        <v>616.3168380011479</v>
+        <v>749.1071739837167</v>
       </c>
       <c r="E24" t="n">
-        <v>594.4258307062867</v>
+        <v>402.9737424464312</v>
       </c>
       <c r="F24" t="n">
-        <v>384.1492552364546</v>
+        <v>59.9068309940303</v>
       </c>
       <c r="G24" t="n">
-        <v>380.1201071256017</v>
+        <v>55.87768288317746</v>
       </c>
       <c r="H24" t="n">
         <v>51.92</v>
@@ -6092,19 +6092,19 @@
         <v>1862.673475647767</v>
       </c>
       <c r="U24" t="n">
-        <v>1458.470472650056</v>
+        <v>1782.71289689248</v>
       </c>
       <c r="V24" t="n">
-        <v>1039.772829022258</v>
+        <v>1688.257677507106</v>
       </c>
       <c r="W24" t="n">
-        <v>927.2747048709159</v>
+        <v>1575.759553355764</v>
       </c>
       <c r="X24" t="n">
-        <v>827.4133518957769</v>
+        <v>1475.898200380625</v>
       </c>
       <c r="Y24" t="n">
-        <v>748.2301268794796</v>
+        <v>1396.714975364328</v>
       </c>
     </row>
     <row r="25">
@@ -6114,28 +6114,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>677.570919560543</v>
+        <v>686.6827231319049</v>
       </c>
       <c r="C25" t="n">
-        <v>725.3629253789787</v>
+        <v>734.4747289503407</v>
       </c>
       <c r="D25" t="n">
-        <v>760.4720695039788</v>
+        <v>769.5838730753408</v>
       </c>
       <c r="E25" t="n">
-        <v>800.0909737153918</v>
+        <v>809.2027772867538</v>
       </c>
       <c r="F25" t="n">
-        <v>846.2419463073272</v>
+        <v>855.3537498786892</v>
       </c>
       <c r="G25" t="n">
-        <v>922.0615630138847</v>
+        <v>931.1733665852466</v>
       </c>
       <c r="H25" t="n">
-        <v>1018.907636370004</v>
+        <v>1028.019439941366</v>
       </c>
       <c r="I25" t="n">
-        <v>1180.567352683136</v>
+        <v>1189.679156254498</v>
       </c>
       <c r="J25" t="n">
         <v>1507.490786286407</v>
@@ -6171,19 +6171,19 @@
         <v>164.447805388313</v>
       </c>
       <c r="U25" t="n">
-        <v>323.7111790454016</v>
+        <v>332.8229826167636</v>
       </c>
       <c r="V25" t="n">
-        <v>444.3225719313476</v>
+        <v>453.4343755027096</v>
       </c>
       <c r="W25" t="n">
-        <v>538.003490191025</v>
+        <v>547.115293762387</v>
       </c>
       <c r="X25" t="n">
-        <v>610.8242812152185</v>
+        <v>619.9360847865805</v>
       </c>
       <c r="Y25" t="n">
-        <v>644.0235818942508</v>
+        <v>653.1353854656128</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>593.5929499013407</v>
+        <v>601.6737579821468</v>
       </c>
       <c r="C26" t="n">
-        <v>471.7853149789834</v>
+        <v>471.9014567265973</v>
       </c>
       <c r="D26" t="n">
-        <v>380.5336425144886</v>
+        <v>381.6598852722036</v>
       </c>
       <c r="E26" t="n">
-        <v>295.3181984671465</v>
+        <v>292.2878954368435</v>
       </c>
       <c r="F26" t="n">
-        <v>209.5710987620841</v>
+        <v>207.5508967418821</v>
       </c>
       <c r="G26" t="n">
-        <v>126.3848793563878</v>
+        <v>125.3747783462868</v>
       </c>
       <c r="H26" t="n">
-        <v>52.00000000000003</v>
+        <v>52</v>
       </c>
       <c r="I26" t="n">
-        <v>52.00000000000003</v>
+        <v>52</v>
       </c>
       <c r="J26" t="n">
-        <v>561.1974722838869</v>
+        <v>135.1957830635917</v>
       </c>
       <c r="K26" t="n">
-        <v>737.8815633894145</v>
+        <v>778.6957830635916</v>
       </c>
       <c r="L26" t="n">
-        <v>1381.381563389415</v>
+        <v>1422.195783063592</v>
       </c>
       <c r="M26" t="n">
-        <v>1381.381563389415</v>
+        <v>1422.195783063592</v>
       </c>
       <c r="N26" t="n">
-        <v>2024.881563389415</v>
+        <v>1647.469637376511</v>
       </c>
       <c r="O26" t="n">
-        <v>2400.546421048316</v>
+        <v>1811.952580216753</v>
       </c>
       <c r="P26" t="n">
-        <v>2600.000000000001</v>
+        <v>2011.406159168438</v>
       </c>
       <c r="Q26" t="n">
-        <v>2600.000000000001</v>
+        <v>2600</v>
       </c>
       <c r="R26" t="n">
-        <v>2600.000000000001</v>
+        <v>2600</v>
       </c>
       <c r="S26" t="n">
-        <v>2455.679836593767</v>
+        <v>2456.689937603866</v>
       </c>
       <c r="T26" t="n">
-        <v>2192.514297971442</v>
+        <v>2194.534499991642</v>
       </c>
       <c r="U26" t="n">
-        <v>1860.080908736513</v>
+        <v>1863.111211766814</v>
       </c>
       <c r="V26" t="n">
-        <v>1547.100076244771</v>
+        <v>1551.140480285173</v>
       </c>
       <c r="W26" t="n">
-        <v>1225.510706567047</v>
+        <v>1230.561211617549</v>
       </c>
       <c r="X26" t="n">
-        <v>950.478551556271</v>
+        <v>956.5391576168749</v>
       </c>
       <c r="Y26" t="n">
-        <v>757.2286195534363</v>
+        <v>764.2993266241413</v>
       </c>
     </row>
     <row r="27">
@@ -6272,31 +6272,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1000.273200974099</v>
+        <v>492.6594965526277</v>
       </c>
       <c r="C27" t="n">
-        <v>958.7581378978173</v>
+        <v>452.1545344864466</v>
       </c>
       <c r="D27" t="n">
-        <v>751.2073760039189</v>
+        <v>100.7023254988682</v>
       </c>
       <c r="E27" t="n">
-        <v>405.0739444666333</v>
+        <v>78.81131820400694</v>
       </c>
       <c r="F27" t="n">
-        <v>385.2393562465556</v>
+        <v>59.9868309940303</v>
       </c>
       <c r="G27" t="n">
-        <v>380.2001071256018</v>
+        <v>55.95768288317746</v>
       </c>
       <c r="H27" t="n">
-        <v>52.00000000000003</v>
+        <v>52</v>
       </c>
       <c r="I27" t="n">
-        <v>52.00000000000003</v>
+        <v>52</v>
       </c>
       <c r="J27" t="n">
-        <v>246.1700193262424</v>
+        <v>246.1700193262423</v>
       </c>
       <c r="K27" t="n">
         <v>555.3688889111918</v>
@@ -6320,28 +6320,28 @@
         <v>2259.337615368536</v>
       </c>
       <c r="R27" t="n">
-        <v>1753.614549683457</v>
+        <v>1886.404885666026</v>
       </c>
       <c r="S27" t="n">
-        <v>1619.654486826121</v>
+        <v>1753.454923818791</v>
       </c>
       <c r="T27" t="n">
-        <v>1536.490849385141</v>
+        <v>1671.301387387912</v>
       </c>
       <c r="U27" t="n">
-        <v>1455.520169619753</v>
+        <v>1591.340808632625</v>
       </c>
       <c r="V27" t="n">
-        <v>1360.054849224278</v>
+        <v>1172.643165004827</v>
       </c>
       <c r="W27" t="n">
-        <v>1246.546624062835</v>
+        <v>1060.145040853485</v>
       </c>
       <c r="X27" t="n">
-        <v>1145.675170077595</v>
+        <v>960.2836878783459</v>
       </c>
       <c r="Y27" t="n">
-        <v>1065.481844051197</v>
+        <v>881.1004628620485</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>679.832723131905</v>
+        <v>677.6509195605429</v>
       </c>
       <c r="C28" t="n">
-        <v>726.6347289503408</v>
+        <v>725.4429253789787</v>
       </c>
       <c r="D28" t="n">
-        <v>760.7538730753408</v>
+        <v>760.5520695039787</v>
       </c>
       <c r="E28" t="n">
-        <v>799.3827772867538</v>
+        <v>800.1709737153917</v>
       </c>
       <c r="F28" t="n">
-        <v>844.5437498786894</v>
+        <v>846.3219463073272</v>
       </c>
       <c r="G28" t="n">
-        <v>919.3733665852473</v>
+        <v>922.1415630138846</v>
       </c>
       <c r="H28" t="n">
-        <v>1015.229439941366</v>
+        <v>1018.987636370003</v>
       </c>
       <c r="I28" t="n">
-        <v>1175.899156254498</v>
+        <v>1180.647352683136</v>
       </c>
       <c r="J28" t="n">
-        <v>1501.832589857769</v>
+        <v>1507.570786286406</v>
       </c>
       <c r="K28" t="n">
-        <v>1605.384200843818</v>
+        <v>1612.112397272455</v>
       </c>
       <c r="L28" t="n">
-        <v>1605.384200843818</v>
+        <v>1603.04037677859</v>
       </c>
       <c r="M28" t="n">
-        <v>1507.101954928026</v>
+        <v>1501.04134886742</v>
       </c>
       <c r="N28" t="n">
-        <v>1350.659289063268</v>
+        <v>1345.608784012762</v>
       </c>
       <c r="O28" t="n">
-        <v>1116.830386781103</v>
+        <v>1112.789982740699</v>
       </c>
       <c r="P28" t="n">
-        <v>822.5560741958252</v>
+        <v>819.525771165522</v>
       </c>
       <c r="Q28" t="n">
-        <v>465.8487343719888</v>
+        <v>463.8285323517866</v>
       </c>
       <c r="R28" t="n">
-        <v>83.72295515605536</v>
+        <v>82.71285414595431</v>
       </c>
       <c r="S28" t="n">
-        <v>52.00000000000003</v>
+        <v>52</v>
       </c>
       <c r="T28" t="n">
-        <v>163.5378053883131</v>
+        <v>164.5278053883131</v>
       </c>
       <c r="U28" t="n">
-        <v>330.9229826167636</v>
+        <v>332.9029826167637</v>
       </c>
       <c r="V28" t="n">
-        <v>450.5443755027096</v>
+        <v>444.4025719313475</v>
       </c>
       <c r="W28" t="n">
-        <v>543.2352937623871</v>
+        <v>538.0834901910249</v>
       </c>
       <c r="X28" t="n">
-        <v>615.0660847865806</v>
+        <v>610.9042812152185</v>
       </c>
       <c r="Y28" t="n">
-        <v>647.2753854656129</v>
+        <v>644.1035818942507</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>601.6737579821481</v>
+        <v>596.5071111840277</v>
       </c>
       <c r="C29" t="n">
-        <v>471.9014567265987</v>
+        <v>466.7348099284783</v>
       </c>
       <c r="D29" t="n">
-        <v>381.6598852722049</v>
+        <v>376.4932384740846</v>
       </c>
       <c r="E29" t="n">
-        <v>297.4545422349639</v>
+        <v>292.2878954368435</v>
       </c>
       <c r="F29" t="n">
-        <v>212.7175435400024</v>
+        <v>207.5508967418821</v>
       </c>
       <c r="G29" t="n">
-        <v>130.5414251444071</v>
+        <v>125.3747783462868</v>
       </c>
       <c r="H29" t="n">
-        <v>57.16664679812028</v>
+        <v>52</v>
       </c>
       <c r="I29" t="n">
-        <v>52.00000000000003</v>
+        <v>52</v>
       </c>
       <c r="J29" t="n">
-        <v>561.1974722838869</v>
+        <v>135.1957830635917</v>
       </c>
       <c r="K29" t="n">
-        <v>737.8815633894145</v>
+        <v>311.8798741691194</v>
       </c>
       <c r="L29" t="n">
-        <v>1381.381563389415</v>
+        <v>531.0721126615816</v>
       </c>
       <c r="M29" t="n">
-        <v>1792.01705715976</v>
+        <v>1174.572112661582</v>
       </c>
       <c r="N29" t="n">
-        <v>1792.01705715976</v>
+        <v>1818.072112661582</v>
       </c>
       <c r="O29" t="n">
-        <v>1956.500000000001</v>
+        <v>1982.555055501823</v>
       </c>
       <c r="P29" t="n">
-        <v>2600.000000000001</v>
+        <v>2182.008634453508</v>
       </c>
       <c r="Q29" t="n">
-        <v>2600.000000000001</v>
+        <v>2600</v>
       </c>
       <c r="R29" t="n">
-        <v>2600.000000000001</v>
+        <v>2594.833353201881</v>
       </c>
       <c r="S29" t="n">
-        <v>2456.689937603868</v>
+        <v>2451.523290805747</v>
       </c>
       <c r="T29" t="n">
-        <v>2194.534499991644</v>
+        <v>2189.367853193523</v>
       </c>
       <c r="U29" t="n">
-        <v>1863.111211766815</v>
+        <v>1857.944564968695</v>
       </c>
       <c r="V29" t="n">
-        <v>1551.140480285175</v>
+        <v>1545.973833487054</v>
       </c>
       <c r="W29" t="n">
-        <v>1230.561211617551</v>
+        <v>1225.39456481943</v>
       </c>
       <c r="X29" t="n">
-        <v>956.5391576168763</v>
+        <v>951.3725108187559</v>
       </c>
       <c r="Y29" t="n">
-        <v>764.2993266241426</v>
+        <v>759.1326798260222</v>
       </c>
     </row>
     <row r="30">
@@ -6509,31 +6509,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>685.8722553146149</v>
+        <v>1008.354009054907</v>
       </c>
       <c r="C30" t="n">
-        <v>645.3672932484338</v>
+        <v>643.6066227463018</v>
       </c>
       <c r="D30" t="n">
-        <v>618.1575085032797</v>
+        <v>292.1544137587234</v>
       </c>
       <c r="E30" t="n">
-        <v>272.0240769659942</v>
+        <v>78.81131820400694</v>
       </c>
       <c r="F30" t="n">
-        <v>253.1995897560176</v>
+        <v>59.9868309940303</v>
       </c>
       <c r="G30" t="n">
-        <v>249.1704416451647</v>
+        <v>55.95768288317746</v>
       </c>
       <c r="H30" t="n">
-        <v>245.2127587619873</v>
+        <v>52</v>
       </c>
       <c r="I30" t="n">
-        <v>52.00000000000003</v>
+        <v>52</v>
       </c>
       <c r="J30" t="n">
-        <v>246.1700193262424</v>
+        <v>246.1700193262423</v>
       </c>
       <c r="K30" t="n">
         <v>555.3688889111918</v>
@@ -6572,13 +6572,13 @@
         <v>1688.337677507106</v>
       </c>
       <c r="W30" t="n">
-        <v>1251.59712911334</v>
+        <v>1575.839553355764</v>
       </c>
       <c r="X30" t="n">
-        <v>829.2540223979088</v>
+        <v>1475.978200380625</v>
       </c>
       <c r="Y30" t="n">
-        <v>750.0707973816114</v>
+        <v>1396.794975364328</v>
       </c>
     </row>
     <row r="31">
@@ -6588,16 +6588,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>686.7627231319051</v>
+        <v>677.6509195605429</v>
       </c>
       <c r="C31" t="n">
-        <v>734.5547289503409</v>
+        <v>725.4429253789787</v>
       </c>
       <c r="D31" t="n">
-        <v>769.6638730753409</v>
+        <v>760.5520695039787</v>
       </c>
       <c r="E31" t="n">
-        <v>809.2827772867539</v>
+        <v>800.1709737153917</v>
       </c>
       <c r="F31" t="n">
         <v>846.3219463073272</v>
@@ -6636,28 +6636,28 @@
         <v>463.8285323517866</v>
       </c>
       <c r="R31" t="n">
-        <v>82.71285414595434</v>
+        <v>82.71285414595431</v>
       </c>
       <c r="S31" t="n">
-        <v>52.00000000000003</v>
+        <v>52</v>
       </c>
       <c r="T31" t="n">
-        <v>164.5278053883131</v>
+        <v>155.4160018169509</v>
       </c>
       <c r="U31" t="n">
-        <v>332.9029826167637</v>
+        <v>323.7911790454015</v>
       </c>
       <c r="V31" t="n">
-        <v>453.5143755027096</v>
+        <v>444.4025719313475</v>
       </c>
       <c r="W31" t="n">
-        <v>547.1952937623871</v>
+        <v>538.0834901910249</v>
       </c>
       <c r="X31" t="n">
-        <v>620.0160847865807</v>
+        <v>610.9042812152185</v>
       </c>
       <c r="Y31" t="n">
-        <v>653.2153854656129</v>
+        <v>644.1035818942507</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>601.6737579821481</v>
+        <v>601.6737579821468</v>
       </c>
       <c r="C32" t="n">
-        <v>471.9014567265987</v>
+        <v>471.9014567265973</v>
       </c>
       <c r="D32" t="n">
-        <v>381.6598852722049</v>
+        <v>381.6598852722036</v>
       </c>
       <c r="E32" t="n">
-        <v>297.4545422349639</v>
+        <v>297.4545422349625</v>
       </c>
       <c r="F32" t="n">
-        <v>212.7175435400024</v>
+        <v>212.717543540001</v>
       </c>
       <c r="G32" t="n">
-        <v>130.5414251444071</v>
+        <v>130.5414251444058</v>
       </c>
       <c r="H32" t="n">
-        <v>52.00000000000003</v>
+        <v>52</v>
       </c>
       <c r="I32" t="n">
-        <v>52.00000000000003</v>
+        <v>52</v>
       </c>
       <c r="J32" t="n">
-        <v>135.1957830635918</v>
+        <v>135.1957830635917</v>
       </c>
       <c r="K32" t="n">
-        <v>778.695783063592</v>
+        <v>311.8798741691194</v>
       </c>
       <c r="L32" t="n">
-        <v>997.8880215560544</v>
+        <v>531.0721126615816</v>
       </c>
       <c r="M32" t="n">
-        <v>997.8880215560544</v>
+        <v>1003.969637376511</v>
       </c>
       <c r="N32" t="n">
-        <v>1203.423216328198</v>
+        <v>1647.469637376511</v>
       </c>
       <c r="O32" t="n">
-        <v>1367.906159168439</v>
+        <v>1811.952580216753</v>
       </c>
       <c r="P32" t="n">
-        <v>2011.406159168439</v>
+        <v>2011.406159168438</v>
       </c>
       <c r="Q32" t="n">
-        <v>2600.000000000001</v>
+        <v>2600</v>
       </c>
       <c r="R32" t="n">
-        <v>2600.000000000001</v>
+        <v>2600</v>
       </c>
       <c r="S32" t="n">
-        <v>2456.689937603868</v>
+        <v>2456.689937603866</v>
       </c>
       <c r="T32" t="n">
-        <v>2194.534499991644</v>
+        <v>2194.534499991642</v>
       </c>
       <c r="U32" t="n">
-        <v>1863.111211766815</v>
+        <v>1863.111211766814</v>
       </c>
       <c r="V32" t="n">
-        <v>1551.140480285175</v>
+        <v>1551.140480285173</v>
       </c>
       <c r="W32" t="n">
-        <v>1230.561211617551</v>
+        <v>1230.561211617549</v>
       </c>
       <c r="X32" t="n">
-        <v>956.5391576168763</v>
+        <v>956.5391576168749</v>
       </c>
       <c r="Y32" t="n">
-        <v>764.2993266241426</v>
+        <v>764.2993266241413</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>509.0794569416692</v>
+        <v>1332.596433297331</v>
       </c>
       <c r="C33" t="n">
-        <v>468.574494875488</v>
+        <v>1100.639382971295</v>
       </c>
       <c r="D33" t="n">
-        <v>441.3647101303338</v>
+        <v>749.1871739837168</v>
       </c>
       <c r="E33" t="n">
-        <v>419.4737028354726</v>
+        <v>403.0537424464312</v>
       </c>
       <c r="F33" t="n">
-        <v>400.649215625496</v>
+        <v>59.98683099403029</v>
       </c>
       <c r="G33" t="n">
-        <v>396.6200675146431</v>
+        <v>55.95768288317743</v>
       </c>
       <c r="H33" t="n">
-        <v>392.6623846314657</v>
+        <v>52</v>
       </c>
       <c r="I33" t="n">
-        <v>392.6623846314657</v>
+        <v>52</v>
       </c>
       <c r="J33" t="n">
-        <v>586.832403957708</v>
+        <v>246.1700193262423</v>
       </c>
       <c r="K33" t="n">
-        <v>896.0312735426575</v>
+        <v>555.3688889111918</v>
       </c>
       <c r="L33" t="n">
-        <v>1328.744683722763</v>
+        <v>988.0822990912976</v>
       </c>
       <c r="M33" t="n">
-        <v>1603.128175465622</v>
+        <v>1262.465790834157</v>
       </c>
       <c r="N33" t="n">
-        <v>1929.695228846776</v>
+        <v>1589.03284421531</v>
       </c>
       <c r="O33" t="n">
-        <v>2345.557312322947</v>
+        <v>2004.894927691482</v>
       </c>
       <c r="P33" t="n">
-        <v>2600.000000000001</v>
+        <v>2259.337615368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>2600.000000000001</v>
+        <v>2259.337615368536</v>
       </c>
       <c r="R33" t="n">
-        <v>2227.067270297491</v>
+        <v>2077.856973925881</v>
       </c>
       <c r="S33" t="n">
-        <v>2094.117308450257</v>
+        <v>1944.907012078646</v>
       </c>
       <c r="T33" t="n">
-        <v>2011.963772019378</v>
+        <v>1862.753475647767</v>
       </c>
       <c r="U33" t="n">
-        <v>1607.760769021666</v>
+        <v>1782.79289689248</v>
       </c>
       <c r="V33" t="n">
-        <v>1513.305549636292</v>
+        <v>1688.337677507106</v>
       </c>
       <c r="W33" t="n">
-        <v>1400.80742548495</v>
+        <v>1575.839553355764</v>
       </c>
       <c r="X33" t="n">
-        <v>1300.946072509812</v>
+        <v>1475.978200380625</v>
       </c>
       <c r="Y33" t="n">
-        <v>897.5204232510901</v>
+        <v>1396.794975364328</v>
       </c>
     </row>
     <row r="34">
@@ -6825,31 +6825,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>686.7627231319051</v>
+        <v>677.6509195605429</v>
       </c>
       <c r="C34" t="n">
-        <v>734.5547289503409</v>
+        <v>725.4429253789787</v>
       </c>
       <c r="D34" t="n">
-        <v>769.6638730753409</v>
+        <v>760.5520695039787</v>
       </c>
       <c r="E34" t="n">
-        <v>809.2827772867539</v>
+        <v>800.1709737153917</v>
       </c>
       <c r="F34" t="n">
-        <v>855.4337498786894</v>
+        <v>846.3219463073272</v>
       </c>
       <c r="G34" t="n">
-        <v>931.2533665852468</v>
+        <v>922.1415630138846</v>
       </c>
       <c r="H34" t="n">
-        <v>1028.099439941366</v>
+        <v>1018.987636370003</v>
       </c>
       <c r="I34" t="n">
-        <v>1189.759156254498</v>
+        <v>1180.647352683136</v>
       </c>
       <c r="J34" t="n">
-        <v>1516.682589857769</v>
+        <v>1507.570786286406</v>
       </c>
       <c r="K34" t="n">
         <v>1612.112397272455</v>
@@ -6873,28 +6873,28 @@
         <v>463.8285323517867</v>
       </c>
       <c r="R34" t="n">
-        <v>82.71285414595435</v>
+        <v>82.71285414595432</v>
       </c>
       <c r="S34" t="n">
-        <v>52.00000000000003</v>
+        <v>52</v>
       </c>
       <c r="T34" t="n">
         <v>164.5278053883131</v>
       </c>
       <c r="U34" t="n">
-        <v>332.9029826167637</v>
+        <v>323.7911790454015</v>
       </c>
       <c r="V34" t="n">
-        <v>453.5143755027096</v>
+        <v>444.4025719313475</v>
       </c>
       <c r="W34" t="n">
-        <v>547.1952937623871</v>
+        <v>538.0834901910249</v>
       </c>
       <c r="X34" t="n">
-        <v>620.0160847865807</v>
+        <v>610.9042812152185</v>
       </c>
       <c r="Y34" t="n">
-        <v>653.2153854656129</v>
+        <v>644.1035818942507</v>
       </c>
     </row>
     <row r="35">
@@ -6907,10 +6907,10 @@
         <v>444.0925657294823</v>
       </c>
       <c r="C35" t="n">
-        <v>338.5626887163571</v>
+        <v>338.5626887163572</v>
       </c>
       <c r="D35" t="n">
-        <v>272.5635415043876</v>
+        <v>272.5635415043877</v>
       </c>
       <c r="E35" t="n">
         <v>212.6006227095708</v>
@@ -6919,7 +6919,7 @@
         <v>152.1060482570336</v>
       </c>
       <c r="G35" t="n">
-        <v>94.17235410386252</v>
+        <v>94.17235410386255</v>
       </c>
       <c r="H35" t="n">
         <v>45.04</v>
@@ -6934,19 +6934,19 @@
         <v>304.9198741691194</v>
       </c>
       <c r="L35" t="n">
-        <v>524.1121126615817</v>
+        <v>773.3234782080734</v>
       </c>
       <c r="M35" t="n">
-        <v>972.7770571597588</v>
+        <v>1330.693478208073</v>
       </c>
       <c r="N35" t="n">
-        <v>972.7770571597588</v>
+        <v>1888.063478208073</v>
       </c>
       <c r="O35" t="n">
-        <v>1137.26</v>
+        <v>2052.546421048315</v>
       </c>
       <c r="P35" t="n">
-        <v>1694.63</v>
+        <v>2252</v>
       </c>
       <c r="Q35" t="n">
         <v>2252</v>
@@ -6961,13 +6961,13 @@
         <v>1895.019348476491</v>
       </c>
       <c r="U35" t="n">
-        <v>1587.838484494087</v>
+        <v>1584.317898302028</v>
       </c>
       <c r="V35" t="n">
-        <v>1300.110177254871</v>
+        <v>1296.589591062812</v>
       </c>
       <c r="W35" t="n">
-        <v>1003.773332829671</v>
+        <v>1000.252746637612</v>
       </c>
       <c r="X35" t="n">
         <v>750.4731168793621</v>
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>497.9860906560681</v>
+        <v>1087.088285474223</v>
       </c>
       <c r="C36" t="n">
-        <v>481.7235528323113</v>
+        <v>722.3408991656172</v>
       </c>
       <c r="D36" t="n">
-        <v>130.2713438447328</v>
+        <v>719.3735386628873</v>
       </c>
       <c r="E36" t="n">
-        <v>130.2713438447328</v>
+        <v>373.2401071256018</v>
       </c>
       <c r="F36" t="n">
-        <v>130.2713438447328</v>
+        <v>373.2401071256018</v>
       </c>
       <c r="G36" t="n">
-        <v>45.04</v>
+        <v>373.2401071256018</v>
       </c>
       <c r="H36" t="n">
         <v>45.04</v>
@@ -7019,7 +7019,7 @@
         <v>1255.505790834157</v>
       </c>
       <c r="N36" t="n">
-        <v>1582.07284421531</v>
+        <v>1581.695228846775</v>
       </c>
       <c r="O36" t="n">
         <v>1997.557312322946</v>
@@ -7040,19 +7040,19 @@
         <v>1928.143133006504</v>
       </c>
       <c r="U36" t="n">
-        <v>1872.424978493641</v>
+        <v>1764.557476342099</v>
       </c>
       <c r="V36" t="n">
-        <v>1453.727334865843</v>
+        <v>1694.344681199149</v>
       </c>
       <c r="W36" t="n">
-        <v>1365.471634956925</v>
+        <v>1257.604132805383</v>
       </c>
       <c r="X36" t="n">
-        <v>941.3678577393621</v>
+        <v>1181.985204072668</v>
       </c>
       <c r="Y36" t="n">
-        <v>886.427056965489</v>
+        <v>1127.044403298795</v>
       </c>
     </row>
     <row r="37">
@@ -7062,34 +7062,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>539.72090755813</v>
+        <v>747.9335403557561</v>
       </c>
       <c r="C37" t="n">
-        <v>611.2729133765657</v>
+        <v>819.4855461741919</v>
       </c>
       <c r="D37" t="n">
-        <v>670.1420575015658</v>
+        <v>878.3546902991919</v>
       </c>
       <c r="E37" t="n">
-        <v>733.5209617129788</v>
+        <v>941.7335945106049</v>
       </c>
       <c r="F37" t="n">
-        <v>803.4319343049142</v>
+        <v>1011.64456710254</v>
       </c>
       <c r="G37" t="n">
-        <v>903.0115510114716</v>
+        <v>1111.224183809098</v>
       </c>
       <c r="H37" t="n">
-        <v>1023.61762436759</v>
+        <v>1231.830257165217</v>
       </c>
       <c r="I37" t="n">
-        <v>1209.037340680723</v>
+        <v>1417.249973478349</v>
       </c>
       <c r="J37" t="n">
-        <v>1411.514894367657</v>
+        <v>1426.38340708162</v>
       </c>
       <c r="K37" t="n">
-        <v>1411.514894367657</v>
+        <v>1426.38340708162</v>
       </c>
       <c r="L37" t="n">
         <v>1426.38340708162</v>
@@ -7107,10 +7107,10 @@
         <v>739.8384984382493</v>
       </c>
       <c r="Q37" t="n">
-        <v>408.3836838669382</v>
+        <v>408.3836838669381</v>
       </c>
       <c r="R37" t="n">
-        <v>51.51042990353008</v>
+        <v>51.51042990353006</v>
       </c>
       <c r="S37" t="n">
         <v>45.04</v>
@@ -7119,19 +7119,19 @@
         <v>181.327805388313</v>
       </c>
       <c r="U37" t="n">
-        <v>181.327805388313</v>
+        <v>275.2737998406148</v>
       </c>
       <c r="V37" t="n">
-        <v>325.699198274259</v>
+        <v>419.6451927265608</v>
       </c>
       <c r="W37" t="n">
-        <v>443.1401165339364</v>
+        <v>537.0861109862382</v>
       </c>
       <c r="X37" t="n">
-        <v>539.72090755813</v>
+        <v>633.6669020104317</v>
       </c>
       <c r="Y37" t="n">
-        <v>539.72090755813</v>
+        <v>690.626202689464</v>
       </c>
     </row>
     <row r="38">
@@ -7141,22 +7141,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>444.0925657294823</v>
+        <v>447.6131519215412</v>
       </c>
       <c r="C38" t="n">
-        <v>338.5626887163571</v>
+        <v>342.083274908416</v>
       </c>
       <c r="D38" t="n">
-        <v>272.5635415043876</v>
+        <v>276.0841276964465</v>
       </c>
       <c r="E38" t="n">
-        <v>212.6006227095708</v>
+        <v>216.1212089016297</v>
       </c>
       <c r="F38" t="n">
-        <v>152.1060482570336</v>
+        <v>155.6266344490924</v>
       </c>
       <c r="G38" t="n">
-        <v>94.17235410386252</v>
+        <v>97.6929402959214</v>
       </c>
       <c r="H38" t="n">
         <v>45.04</v>
@@ -7165,13 +7165,13 @@
         <v>45.04</v>
       </c>
       <c r="J38" t="n">
-        <v>215.9534782080734</v>
+        <v>128.2357830635917</v>
       </c>
       <c r="K38" t="n">
+        <v>304.9198741691194</v>
+      </c>
+      <c r="L38" t="n">
         <v>773.3234782080734</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1330.693478208073</v>
       </c>
       <c r="M38" t="n">
         <v>1330.693478208073</v>
@@ -7189,28 +7189,28 @@
         <v>2252</v>
       </c>
       <c r="R38" t="n">
-        <v>2248.479413807941</v>
+        <v>2252</v>
       </c>
       <c r="S38" t="n">
-        <v>2129.411775654232</v>
+        <v>2132.932361846291</v>
       </c>
       <c r="T38" t="n">
-        <v>1891.498762284433</v>
+        <v>1895.019348476491</v>
       </c>
       <c r="U38" t="n">
-        <v>1584.317898302028</v>
+        <v>1587.838484494087</v>
       </c>
       <c r="V38" t="n">
-        <v>1296.589591062812</v>
+        <v>1300.110177254871</v>
       </c>
       <c r="W38" t="n">
-        <v>1000.252746637612</v>
+        <v>1003.773332829671</v>
       </c>
       <c r="X38" t="n">
-        <v>750.4731168793621</v>
+        <v>753.9937030714209</v>
       </c>
       <c r="Y38" t="n">
-        <v>582.4757101290526</v>
+        <v>585.9962963211115</v>
       </c>
     </row>
     <row r="39">
@@ -7220,25 +7220,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>497.9860906560681</v>
+        <v>1104.306506748585</v>
       </c>
       <c r="C39" t="n">
-        <v>481.7235528323113</v>
+        <v>739.5591204399793</v>
       </c>
       <c r="D39" t="n">
-        <v>478.7561923295813</v>
+        <v>388.1069114524009</v>
       </c>
       <c r="E39" t="n">
-        <v>478.7561923295813</v>
+        <v>388.1069114524009</v>
       </c>
       <c r="F39" t="n">
-        <v>135.6892808771804</v>
+        <v>45.04</v>
       </c>
       <c r="G39" t="n">
-        <v>135.6892808771804</v>
+        <v>45.04</v>
       </c>
       <c r="H39" t="n">
-        <v>135.6892808771804</v>
+        <v>45.04</v>
       </c>
       <c r="I39" t="n">
         <v>45.04</v>
@@ -7250,46 +7250,46 @@
         <v>548.4088889111918</v>
       </c>
       <c r="L39" t="n">
-        <v>980.7446837227624</v>
+        <v>980.7446837228083</v>
       </c>
       <c r="M39" t="n">
-        <v>1255.128175465622</v>
+        <v>1255.128175465667</v>
       </c>
       <c r="N39" t="n">
-        <v>1581.695228846775</v>
+        <v>1581.695228846821</v>
       </c>
       <c r="O39" t="n">
-        <v>1997.557312322946</v>
+        <v>1997.557312322992</v>
       </c>
       <c r="P39" t="n">
-        <v>2252</v>
+        <v>2252.000000000046</v>
       </c>
       <c r="Q39" t="n">
-        <v>2252</v>
+        <v>2252.000000000046</v>
       </c>
       <c r="R39" t="n">
-        <v>1746.276934314921</v>
+        <v>1746.276934314967</v>
       </c>
       <c r="S39" t="n">
-        <v>1637.56939671011</v>
+        <v>1546.92011583293</v>
       </c>
       <c r="T39" t="n">
-        <v>1579.658284521655</v>
+        <v>1489.009003644475</v>
       </c>
       <c r="U39" t="n">
-        <v>1523.940130008793</v>
+        <v>1433.290849131612</v>
       </c>
       <c r="V39" t="n">
-        <v>1453.727334865843</v>
+        <v>1363.078053988663</v>
       </c>
       <c r="W39" t="n">
-        <v>1365.471634956925</v>
+        <v>1274.822354079745</v>
       </c>
       <c r="X39" t="n">
-        <v>941.3678577393621</v>
+        <v>1199.20342534703</v>
       </c>
       <c r="Y39" t="n">
-        <v>886.427056965489</v>
+        <v>1144.262624573157</v>
       </c>
     </row>
     <row r="40">
@@ -7299,31 +7299,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>565.4635248576459</v>
+        <v>604.7634166557448</v>
       </c>
       <c r="C40" t="n">
-        <v>565.4635248576459</v>
+        <v>676.3154224741805</v>
       </c>
       <c r="D40" t="n">
-        <v>624.3326689826459</v>
+        <v>735.1845665991806</v>
       </c>
       <c r="E40" t="n">
-        <v>687.7115731940589</v>
+        <v>798.5634708105936</v>
       </c>
       <c r="F40" t="n">
-        <v>757.6225457859944</v>
+        <v>868.4744434025291</v>
       </c>
       <c r="G40" t="n">
-        <v>857.2021624925518</v>
+        <v>968.0540601090865</v>
       </c>
       <c r="H40" t="n">
-        <v>857.2021624925518</v>
+        <v>1088.660133465205</v>
       </c>
       <c r="I40" t="n">
-        <v>1042.621878805684</v>
+        <v>1274.079849778338</v>
       </c>
       <c r="J40" t="n">
-        <v>1393.305312408955</v>
+        <v>1283.213283381609</v>
       </c>
       <c r="K40" t="n">
         <v>1411.514894367657</v>
@@ -7353,22 +7353,22 @@
         <v>45.04</v>
       </c>
       <c r="T40" t="n">
-        <v>45.04</v>
+        <v>181.327805388313</v>
       </c>
       <c r="U40" t="n">
-        <v>237.1751772284506</v>
+        <v>276.4750690265495</v>
       </c>
       <c r="V40" t="n">
-        <v>237.1751772284506</v>
+        <v>276.4750690265495</v>
       </c>
       <c r="W40" t="n">
-        <v>354.616095488128</v>
+        <v>393.9159872862269</v>
       </c>
       <c r="X40" t="n">
-        <v>451.1968865123215</v>
+        <v>490.4967783104204</v>
       </c>
       <c r="Y40" t="n">
-        <v>508.1561871913538</v>
+        <v>547.4560789894526</v>
       </c>
     </row>
     <row r="41">
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>589.5471111840278</v>
+        <v>265.0538727099432</v>
       </c>
       <c r="C41" t="n">
-        <v>459.7748099284784</v>
+        <v>135.2815714543937</v>
       </c>
       <c r="D41" t="n">
-        <v>369.5332384740846</v>
+        <v>45.04</v>
       </c>
       <c r="E41" t="n">
-        <v>285.3278954368436</v>
+        <v>45.04</v>
       </c>
       <c r="F41" t="n">
-        <v>200.5908967418821</v>
+        <v>45.04</v>
       </c>
       <c r="G41" t="n">
-        <v>118.4147783462868</v>
+        <v>45.04</v>
       </c>
       <c r="H41" t="n">
         <v>45.04</v>
@@ -7408,10 +7408,10 @@
         <v>304.9198741691194</v>
       </c>
       <c r="L41" t="n">
-        <v>862.2898741691193</v>
+        <v>524.1121126615817</v>
       </c>
       <c r="M41" t="n">
-        <v>862.2898741691195</v>
+        <v>1081.482112661582</v>
       </c>
       <c r="N41" t="n">
         <v>1330.693478208073</v>
@@ -7435,19 +7435,19 @@
         <v>1846.534499991642</v>
       </c>
       <c r="U41" t="n">
-        <v>1515.111211766814</v>
+        <v>1526.49132649461</v>
       </c>
       <c r="V41" t="n">
-        <v>1203.140480285173</v>
+        <v>1214.52059501297</v>
       </c>
       <c r="W41" t="n">
-        <v>882.5612116175494</v>
+        <v>893.9413263453457</v>
       </c>
       <c r="X41" t="n">
-        <v>781.7869421767616</v>
+        <v>619.9192723446713</v>
       </c>
       <c r="Y41" t="n">
-        <v>589.5471111840278</v>
+        <v>427.6794413519376</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1134.184345037476</v>
+        <v>1001.016393686372</v>
       </c>
       <c r="C42" t="n">
-        <v>1093.679382971295</v>
+        <v>636.2690073777662</v>
       </c>
       <c r="D42" t="n">
-        <v>1066.469598226141</v>
+        <v>609.0592226326121</v>
       </c>
       <c r="E42" t="n">
-        <v>720.3361666888554</v>
+        <v>262.9257910953266</v>
       </c>
       <c r="F42" t="n">
-        <v>377.2692552364546</v>
+        <v>244.1013038853499</v>
       </c>
       <c r="G42" t="n">
-        <v>48.99768288317746</v>
+        <v>240.0721557744971</v>
       </c>
       <c r="H42" t="n">
         <v>45.04</v>
@@ -7502,31 +7502,31 @@
         <v>2252</v>
       </c>
       <c r="Q42" t="n">
-        <v>2173.963921292254</v>
+        <v>2252</v>
       </c>
       <c r="R42" t="n">
-        <v>1992.4832798496</v>
+        <v>2070.519358557345</v>
       </c>
       <c r="S42" t="n">
-        <v>1859.533318002365</v>
+        <v>1937.569396710111</v>
       </c>
       <c r="T42" t="n">
-        <v>1664.341387387912</v>
+        <v>1855.415860279231</v>
       </c>
       <c r="U42" t="n">
-        <v>1584.380808632625</v>
+        <v>1775.455281523944</v>
       </c>
       <c r="V42" t="n">
-        <v>1489.925589247251</v>
+        <v>1681.00006213857</v>
       </c>
       <c r="W42" t="n">
-        <v>1377.427465095909</v>
+        <v>1244.259513744804</v>
       </c>
       <c r="X42" t="n">
-        <v>1277.56611212077</v>
+        <v>1144.398160769665</v>
       </c>
       <c r="Y42" t="n">
-        <v>1198.382887104473</v>
+        <v>1065.214935753368</v>
       </c>
     </row>
     <row r="43">
@@ -7536,28 +7536,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>670.6909195605429</v>
+        <v>679.8027231319051</v>
       </c>
       <c r="C43" t="n">
-        <v>718.4829253789786</v>
+        <v>727.5947289503408</v>
       </c>
       <c r="D43" t="n">
-        <v>753.5920695039787</v>
+        <v>762.7038730753409</v>
       </c>
       <c r="E43" t="n">
-        <v>793.2109737153917</v>
+        <v>802.3227772867539</v>
       </c>
       <c r="F43" t="n">
-        <v>839.3619463073271</v>
+        <v>848.4737498786893</v>
       </c>
       <c r="G43" t="n">
-        <v>915.1815630138846</v>
+        <v>924.2933665852468</v>
       </c>
       <c r="H43" t="n">
-        <v>1012.027636370003</v>
+        <v>1021.139439941366</v>
       </c>
       <c r="I43" t="n">
-        <v>1173.687352683135</v>
+        <v>1182.799156254498</v>
       </c>
       <c r="J43" t="n">
         <v>1500.610786286406</v>
@@ -7590,22 +7590,22 @@
         <v>45.04</v>
       </c>
       <c r="T43" t="n">
-        <v>148.4560018169509</v>
+        <v>157.567805388313</v>
       </c>
       <c r="U43" t="n">
-        <v>316.8311790454015</v>
+        <v>325.9429826167636</v>
       </c>
       <c r="V43" t="n">
-        <v>437.4425719313475</v>
+        <v>446.5543755027096</v>
       </c>
       <c r="W43" t="n">
-        <v>531.1234901910249</v>
+        <v>540.2352937623871</v>
       </c>
       <c r="X43" t="n">
-        <v>603.9442812152184</v>
+        <v>613.0560847865806</v>
       </c>
       <c r="Y43" t="n">
-        <v>637.1435818942507</v>
+        <v>646.2553854656129</v>
       </c>
     </row>
     <row r="44">
@@ -7615,19 +7615,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>527.6958119828212</v>
+        <v>396.9838203782804</v>
       </c>
       <c r="C44" t="n">
-        <v>397.9235107272717</v>
+        <v>396.9838203782804</v>
       </c>
       <c r="D44" t="n">
-        <v>307.681939272878</v>
+        <v>369.5332384740846</v>
       </c>
       <c r="E44" t="n">
-        <v>223.4765962356369</v>
+        <v>285.3278954368435</v>
       </c>
       <c r="F44" t="n">
-        <v>138.7395975406754</v>
+        <v>200.590896741882</v>
       </c>
       <c r="G44" t="n">
         <v>118.4147783462868</v>
@@ -7651,13 +7651,13 @@
         <v>1081.482112661582</v>
       </c>
       <c r="N44" t="n">
-        <v>1495.176421048315</v>
+        <v>1638.852112661581</v>
       </c>
       <c r="O44" t="n">
-        <v>2052.546421048315</v>
+        <v>1803.335055501823</v>
       </c>
       <c r="P44" t="n">
-        <v>2252</v>
+        <v>2002.788634453508</v>
       </c>
       <c r="Q44" t="n">
         <v>2252</v>
@@ -7666,25 +7666,25 @@
         <v>2252</v>
       </c>
       <c r="S44" t="n">
-        <v>2108.689937603866</v>
+        <v>2252</v>
       </c>
       <c r="T44" t="n">
-        <v>1846.534499991642</v>
+        <v>1989.844562387776</v>
       </c>
       <c r="U44" t="n">
-        <v>1515.111211766814</v>
+        <v>1658.421274162947</v>
       </c>
       <c r="V44" t="n">
-        <v>1203.140480285173</v>
+        <v>1346.450542681307</v>
       </c>
       <c r="W44" t="n">
-        <v>882.5612116175494</v>
+        <v>1025.871274013683</v>
       </c>
       <c r="X44" t="n">
-        <v>882.5612116175494</v>
+        <v>751.8492200130086</v>
       </c>
       <c r="Y44" t="n">
-        <v>690.3213806248157</v>
+        <v>559.6093890202749</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>676.7739694439472</v>
+        <v>922.9803149786255</v>
       </c>
       <c r="C45" t="n">
-        <v>636.2690073777661</v>
+        <v>882.4753529124445</v>
       </c>
       <c r="D45" t="n">
-        <v>609.059222632612</v>
+        <v>855.2655681672903</v>
       </c>
       <c r="E45" t="n">
-        <v>396.0937424464312</v>
+        <v>833.3745608724291</v>
       </c>
       <c r="F45" t="n">
-        <v>53.02683099403028</v>
+        <v>490.3076494200282</v>
       </c>
       <c r="G45" t="n">
-        <v>48.99768288317743</v>
+        <v>486.2785013091753</v>
       </c>
       <c r="H45" t="n">
-        <v>45.04</v>
+        <v>238.2527587619873</v>
       </c>
       <c r="I45" t="n">
         <v>45.04</v>
@@ -7730,40 +7730,40 @@
         <v>1255.505790834157</v>
       </c>
       <c r="N45" t="n">
-        <v>1582.07284421531</v>
+        <v>1581.695228846775</v>
       </c>
       <c r="O45" t="n">
-        <v>1997.557312322969</v>
+        <v>1997.557312322946</v>
       </c>
       <c r="P45" t="n">
-        <v>2252.000000000022</v>
+        <v>2252</v>
       </c>
       <c r="Q45" t="n">
-        <v>2252</v>
+        <v>2173.963921292254</v>
       </c>
       <c r="R45" t="n">
-        <v>2070.519358557345</v>
+        <v>1668.240855607175</v>
       </c>
       <c r="S45" t="n">
-        <v>1937.569396710111</v>
+        <v>1535.29089375994</v>
       </c>
       <c r="T45" t="n">
-        <v>1855.415860279231</v>
+        <v>1453.137357329061</v>
       </c>
       <c r="U45" t="n">
-        <v>1775.455281523944</v>
+        <v>1373.176778573774</v>
       </c>
       <c r="V45" t="n">
-        <v>1681.00006213857</v>
+        <v>1278.7215591884</v>
       </c>
       <c r="W45" t="n">
-        <v>1568.501937987229</v>
+        <v>1166.223435037058</v>
       </c>
       <c r="X45" t="n">
-        <v>1468.64058501209</v>
+        <v>1066.362082061919</v>
       </c>
       <c r="Y45" t="n">
-        <v>1065.214935753368</v>
+        <v>987.1788570456221</v>
       </c>
     </row>
     <row r="46">
@@ -7773,28 +7773,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>679.8027231319051</v>
+        <v>670.6909195605429</v>
       </c>
       <c r="C46" t="n">
-        <v>727.5947289503408</v>
+        <v>718.4829253789786</v>
       </c>
       <c r="D46" t="n">
-        <v>762.7038730753409</v>
+        <v>753.5920695039787</v>
       </c>
       <c r="E46" t="n">
-        <v>802.3227772867539</v>
+        <v>793.2109737153917</v>
       </c>
       <c r="F46" t="n">
-        <v>848.4737498786893</v>
+        <v>839.3619463073271</v>
       </c>
       <c r="G46" t="n">
-        <v>924.2933665852468</v>
+        <v>915.1815630138846</v>
       </c>
       <c r="H46" t="n">
-        <v>1021.139439941366</v>
+        <v>1012.027636370003</v>
       </c>
       <c r="I46" t="n">
-        <v>1182.799156254498</v>
+        <v>1173.687352683135</v>
       </c>
       <c r="J46" t="n">
         <v>1500.610786286406</v>
@@ -7830,19 +7830,19 @@
         <v>157.5678053883131</v>
       </c>
       <c r="U46" t="n">
-        <v>325.9429826167636</v>
+        <v>316.8311790454015</v>
       </c>
       <c r="V46" t="n">
-        <v>446.5543755027096</v>
+        <v>437.4425719313475</v>
       </c>
       <c r="W46" t="n">
-        <v>540.2352937623871</v>
+        <v>531.1234901910249</v>
       </c>
       <c r="X46" t="n">
-        <v>613.0560847865806</v>
+        <v>603.9442812152184</v>
       </c>
       <c r="Y46" t="n">
-        <v>646.2553854656129</v>
+        <v>637.1435818942507</v>
       </c>
     </row>
   </sheetData>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>373.5581017224773</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>320.8173266331657</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>181.5167089435048</v>
       </c>
       <c r="M2" t="n">
-        <v>470.8491025166892</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N2" t="n">
-        <v>402.6480334467196</v>
+        <v>777.3653500296342</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P2" t="n">
-        <v>232.8805421217533</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>501.6736190008522</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8052,7 +8052,7 @@
         <v>388.0893364597981</v>
       </c>
       <c r="M3" t="n">
-        <v>468.8522544012835</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N3" t="n">
         <v>485.4085271713503</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>373.5581017224773</v>
       </c>
       <c r="K5" t="n">
-        <v>320.8173266331659</v>
+        <v>320.8173266331657</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>308.0221909547739</v>
       </c>
       <c r="M5" t="n">
-        <v>703.4834144752695</v>
+        <v>470.8491025166892</v>
       </c>
       <c r="N5" t="n">
         <v>402.6480334467196</v>
       </c>
       <c r="O5" t="n">
-        <v>373.8043318856502</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>501.6736190008522</v>
+        <v>426.5319701678315</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,19 +8438,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>373.5581017224773</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>320.8173266331657</v>
+        <v>320.8173266331659</v>
       </c>
       <c r="L8" t="n">
         <v>308.0221909547739</v>
       </c>
       <c r="M8" t="n">
-        <v>470.8491025166892</v>
+        <v>769.2655554061457</v>
       </c>
       <c r="N8" t="n">
-        <v>701.5063846136989</v>
+        <v>776.6480334467196</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -8526,13 +8526,13 @@
         <v>388.0893364597981</v>
       </c>
       <c r="M9" t="n">
-        <v>468.8522544012835</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N9" t="n">
         <v>485.4085271713503</v>
       </c>
       <c r="O9" t="n">
-        <v>382.6817988009037</v>
+        <v>379.8392327720798</v>
       </c>
       <c r="P9" t="n">
         <v>219.1507118405495</v>
@@ -8678,16 +8678,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>470.5312211055276</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>427.5936984924624</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>687.7292051963152</v>
+        <v>342.3148916311111</v>
       </c>
       <c r="N11" t="n">
-        <v>226.9054706326493</v>
+        <v>875.9054706326493</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>21.31284010637989</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,25 +8915,25 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>470.5312211055276</v>
       </c>
       <c r="L14" t="n">
-        <v>427.5936984924623</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>946.9049567880461</v>
+        <v>302.0884071117403</v>
       </c>
       <c r="N14" t="n">
-        <v>226.9054706326493</v>
+        <v>875.9054706326493</v>
       </c>
       <c r="O14" t="n">
-        <v>194.1284676673123</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>447.5317384326413</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>21.31284010637989</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,16 +9152,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>470.5312211055276</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>427.5936984924624</v>
       </c>
       <c r="M17" t="n">
-        <v>297.904956788046</v>
+        <v>509.2604263018426</v>
       </c>
       <c r="N17" t="n">
-        <v>226.9054706326493</v>
+        <v>875.9054706326493</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>411.1370885146491</v>
+        <v>21.31284010637989</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,7 +9386,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -9398,16 +9398,16 @@
         <v>946.9049567880461</v>
       </c>
       <c r="N20" t="n">
-        <v>271.3154054757146</v>
+        <v>813.3037619323798</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>482.8556132926853</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>21.31284010637989</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9629,22 +9629,22 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>427.5936984924624</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>297.904956788046</v>
+        <v>489.3223863616637</v>
       </c>
       <c r="N23" t="n">
-        <v>226.9054706326493</v>
+        <v>875.9054706326493</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>265.8162363506027</v>
+        <v>447.5317384326413</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>21.31284010637989</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,28 +9860,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>471.5312211055276</v>
       </c>
       <c r="L26" t="n">
-        <v>428.5936984924626</v>
+        <v>428.5936984924622</v>
       </c>
       <c r="M26" t="n">
         <v>297.904956788046</v>
       </c>
       <c r="N26" t="n">
-        <v>876.9054706326493</v>
+        <v>454.4548184234775</v>
       </c>
       <c r="O26" t="n">
-        <v>213.3150654733934</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>21.31284010637989</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,28 +10097,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>428.5936984924626</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>712.6882838287983</v>
+        <v>947.9049567880461</v>
       </c>
       <c r="N29" t="n">
-        <v>226.9054706326493</v>
+        <v>876.9054706326493</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>448.5317384326416</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>21.31284010637989</v>
+        <v>443.5263406583916</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,22 +10337,22 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>471.5312211055279</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>297.904956788046</v>
+        <v>775.5792241768638</v>
       </c>
       <c r="N32" t="n">
-        <v>434.5167784832992</v>
+        <v>876.9054706326493</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>448.5317384326418</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10577,22 +10577,22 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>251.7286520671634</v>
       </c>
       <c r="M35" t="n">
-        <v>751.1018704225683</v>
+        <v>860.9049567880461</v>
       </c>
       <c r="N35" t="n">
-        <v>226.9054706326493</v>
+        <v>789.9054706326493</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>361.5317384326413</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>584.3128401063799</v>
+        <v>21.31284010637989</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10662,10 +10662,10 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N36" t="n">
-        <v>485.4085271713503</v>
+        <v>485.0270975061629</v>
       </c>
       <c r="O36" t="n">
-        <v>382.3003691357164</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P36" t="n">
         <v>219.1507118405495</v>
@@ -10808,16 +10808,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>88.60373246917348</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>384.5312211055276</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>341.5936984924623</v>
+        <v>251.7286520671634</v>
       </c>
       <c r="M38" t="n">
-        <v>297.904956788046</v>
+        <v>860.9049567880461</v>
       </c>
       <c r="N38" t="n">
         <v>789.9054706326493</v>
@@ -10893,7 +10893,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>387.7079067946111</v>
+        <v>387.7079067946574</v>
       </c>
       <c r="M39" t="n">
         <v>471.6948204301074</v>
@@ -11051,13 +11051,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>341.5936984924623</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>297.904956788046</v>
+        <v>860.9049567880461</v>
       </c>
       <c r="N41" t="n">
-        <v>700.0404242073503</v>
+        <v>478.6341226998128</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11294,16 +11294,16 @@
         <v>860.9049567880461</v>
       </c>
       <c r="N44" t="n">
-        <v>644.7785094071272</v>
+        <v>789.9054706326493</v>
       </c>
       <c r="O44" t="n">
-        <v>396.8556132926853</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>21.31284010637989</v>
+        <v>273.0414921735436</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11373,10 +11373,10 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N45" t="n">
-        <v>485.4085271713503</v>
+        <v>485.0270975061629</v>
       </c>
       <c r="O45" t="n">
-        <v>382.3003691357389</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P45" t="n">
         <v>219.1507118405495</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1.35003119794419e-12</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -24411,7 +24411,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>8.885019669860142</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -24596,10 +24596,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>9.981300288926704</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.679614175424547</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -25593,7 +25593,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>160.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -25602,16 +25602,16 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>83.36328960686865</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>83.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>81.35435721163935</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>72.64103056282391</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25650,7 +25650,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>11.26631358051833</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -25659,7 +25659,7 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>171.5153067142878</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -25833,10 +25833,10 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>128.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>62.16307965469593</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -25845,7 +25845,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>61.23278620919453</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -25881,7 +25881,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>141.8769617721721</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -25896,7 +25896,7 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>271.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>947935.4672359211</v>
+        <v>948081.4666758077</v>
       </c>
     </row>
     <row r="3">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7747078.675368808</v>
+        <v>7747793.574289992</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8597158.177593308</v>
+        <v>8597873.076514492</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9447237.679817811</v>
+        <v>9447952.578738995</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10289086.03207516</v>
+        <v>10289800.93099634</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11139165.53429967</v>
+        <v>11139880.43322085</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11971379.02600931</v>
+        <v>11972093.9249305</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12803592.51771896</v>
+        <v>12804307.41664014</v>
       </c>
     </row>
   </sheetData>
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1353830.318357539</v>
+        <v>1353830.31835754</v>
       </c>
       <c r="C2" t="n">
         <v>1353830.318357539</v>
@@ -26278,7 +26278,7 @@
         <v>1353830.31835754</v>
       </c>
       <c r="E2" t="n">
-        <v>1353830.31835754</v>
+        <v>1353830.318357539</v>
       </c>
       <c r="F2" t="n">
         <v>1353830.31835754</v>
@@ -26287,19 +26287,19 @@
         <v>1353830.31835754</v>
       </c>
       <c r="H2" t="n">
-        <v>1353830.31835754</v>
+        <v>1353830.318357539</v>
       </c>
       <c r="I2" t="n">
         <v>1353830.31835754</v>
       </c>
       <c r="J2" t="n">
-        <v>1352691.775631209</v>
+        <v>1353830.31835754</v>
       </c>
       <c r="K2" t="n">
         <v>1353830.31835754</v>
       </c>
       <c r="L2" t="n">
-        <v>1353830.318357539</v>
+        <v>1353830.31835754</v>
       </c>
       <c r="M2" t="n">
         <v>1353830.31835754</v>
@@ -26321,10 +26321,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>233048</v>
+        <v>232073</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -26345,25 +26345,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388000.0000000002</v>
+        <v>388800</v>
       </c>
       <c r="K3" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>85375.99999999988</v>
+        <v>85376</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>236800</v>
+        <v>237600</v>
       </c>
       <c r="P3" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>601944.7387873891</v>
+        <v>601967.7658514546</v>
       </c>
       <c r="C4" t="n">
-        <v>599936.6614238161</v>
+        <v>599737.8665118433</v>
       </c>
       <c r="D4" t="n">
-        <v>597925.8599779638</v>
+        <v>597727.0650659911</v>
       </c>
       <c r="E4" t="n">
-        <v>513503.9011844641</v>
+        <v>513306.8786915817</v>
       </c>
       <c r="F4" t="n">
-        <v>511820.5947772248</v>
+        <v>511623.5722843424</v>
       </c>
       <c r="G4" t="n">
-        <v>510134.9654702991</v>
+        <v>509937.9429774167</v>
       </c>
       <c r="H4" t="n">
-        <v>508446.9966060842</v>
+        <v>508249.9741132018</v>
       </c>
       <c r="I4" t="n">
-        <v>506756.6713099375</v>
+        <v>506559.6488170551</v>
       </c>
       <c r="J4" t="n">
-        <v>504401.4226534664</v>
+        <v>504793.4873038072</v>
       </c>
       <c r="K4" t="n">
-        <v>503296.329942291</v>
+        <v>503099.1153601167</v>
       </c>
       <c r="L4" t="n">
-        <v>501599.5506185964</v>
+        <v>501402.3360364221</v>
       </c>
       <c r="M4" t="n">
-        <v>506037.2264392202</v>
+        <v>505856.7334818643</v>
       </c>
       <c r="N4" t="n">
-        <v>504273.0324747441</v>
+        <v>504092.5395173877</v>
       </c>
       <c r="O4" t="n">
-        <v>488192.3996707724</v>
+        <v>488011.9067134165</v>
       </c>
       <c r="P4" t="n">
-        <v>486484.8207461908</v>
+        <v>486304.327788835</v>
       </c>
     </row>
     <row r="5">
@@ -26425,7 +26425,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58634</v>
+        <v>58612.2</v>
       </c>
       <c r="C5" t="n">
         <v>58634</v>
@@ -26449,13 +26449,13 @@
         <v>74053.549</v>
       </c>
       <c r="J5" t="n">
-        <v>74030.28000000003</v>
+        <v>74114.349</v>
       </c>
       <c r="K5" t="n">
-        <v>74114.34900000002</v>
+        <v>74114.349</v>
       </c>
       <c r="L5" t="n">
-        <v>74114.34900000002</v>
+        <v>74114.349</v>
       </c>
       <c r="M5" t="n">
         <v>70842.405</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>460203.5795701502</v>
+        <v>461177.352506085</v>
       </c>
       <c r="C6" t="n">
-        <v>695259.6569337233</v>
+        <v>694483.4518456958</v>
       </c>
       <c r="D6" t="n">
-        <v>697270.458379576</v>
+        <v>697469.2532915487</v>
       </c>
       <c r="E6" t="n">
-        <v>173797.8681730757</v>
+        <v>173994.8906659575</v>
       </c>
       <c r="F6" t="n">
-        <v>767956.1745803152</v>
+        <v>768153.1970731977</v>
       </c>
       <c r="G6" t="n">
-        <v>769641.8038872412</v>
+        <v>769838.8263801236</v>
       </c>
       <c r="H6" t="n">
-        <v>771329.7727514561</v>
+        <v>771526.7952443376</v>
       </c>
       <c r="I6" t="n">
-        <v>773020.0980476026</v>
+        <v>773217.1205404849</v>
       </c>
       <c r="J6" t="n">
-        <v>386260.0729777425</v>
+        <v>386122.4820537331</v>
       </c>
       <c r="K6" t="n">
-        <v>775619.6394152488</v>
+        <v>776616.8539974231</v>
       </c>
       <c r="L6" t="n">
-        <v>778116.4187389427</v>
+        <v>778313.6333211177</v>
       </c>
       <c r="M6" t="n">
-        <v>691574.6869183196</v>
+        <v>691755.1798756757</v>
       </c>
       <c r="N6" t="n">
-        <v>778714.8808827959</v>
+        <v>778895.3738401521</v>
       </c>
       <c r="O6" t="n">
-        <v>531559.8936816175</v>
+        <v>530940.3866389736</v>
       </c>
       <c r="P6" t="n">
-        <v>769267.4726061982</v>
+        <v>770247.9655635543</v>
       </c>
     </row>
   </sheetData>
@@ -26779,7 +26779,7 @@
         <v>321</v>
       </c>
       <c r="J2" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K2" t="n">
         <v>321</v>
@@ -26807,7 +26807,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
         <v>104</v>
@@ -26883,13 +26883,13 @@
         <v>649</v>
       </c>
       <c r="J4" t="n">
-        <v>650.0000000000003</v>
+        <v>650</v>
       </c>
       <c r="K4" t="n">
-        <v>650.0000000000003</v>
+        <v>650</v>
       </c>
       <c r="L4" t="n">
-        <v>650.0000000000003</v>
+        <v>650</v>
       </c>
       <c r="M4" t="n">
         <v>563</v>
@@ -26996,10 +26996,10 @@
         <v>-0</v>
       </c>
       <c r="J2" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
@@ -27008,13 +27008,13 @@
         <v>24</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -27024,10 +27024,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>-0</v>
@@ -27228,10 +27228,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -27448,13 +27448,13 @@
         <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>397.8918749462438</v>
+        <v>400</v>
       </c>
       <c r="H2" t="n">
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>133.9627275218806</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>224.6157244564351</v>
+        <v>222.9148456338331</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27518,7 +27518,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -27527,13 +27527,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
-        <v>209.4244990988957</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27560,7 +27560,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>400</v>
+        <v>261.0604242548132</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>357.8842536949873</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27615,7 +27615,7 @@
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>22.00980129492416</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
@@ -27642,13 +27642,13 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>359.105151834003</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>209.2232550308479</v>
+        <v>244.2466811844738</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9481617662612</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
@@ -27657,7 +27657,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>321.4837699506972</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
         <v>287.4653528494624</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>133.9627275218806</v>
+        <v>131.8546024681244</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>222.5075994026788</v>
+        <v>224.6157244564351</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27752,16 +27752,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>55.4434199793244</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>325.5158377618198</v>
@@ -27770,7 +27770,7 @@
         <v>330.0076343562325</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>209.4244990988957</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>144.5243971659513</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27815,10 +27815,10 @@
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>400</v>
+        <v>45.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>399.3913927661343</v>
+        <v>74.92585735515405</v>
       </c>
     </row>
     <row r="7">
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
         <v>400</v>
@@ -27840,13 +27840,13 @@
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>280.0894497385021</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>244.8563318579235</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>227.103716265553</v>
       </c>
       <c r="I7" t="n">
         <v>170.9935867676593</v>
@@ -27858,7 +27858,7 @@
         <v>266.7319213421267</v>
       </c>
       <c r="L7" t="n">
-        <v>400</v>
+        <v>395.6653986495825</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,13 +27879,13 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>359.105151834003</v>
       </c>
       <c r="T7" t="n">
         <v>209.2232550308479</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9481617662612</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
         <v>400</v>
@@ -27894,7 +27894,7 @@
         <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>268.7580862422242</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
         <v>400</v>
@@ -27925,7 +27925,7 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>400</v>
+        <v>397.8918749462438</v>
       </c>
       <c r="I8" t="n">
         <v>133.9627275218806</v>
@@ -27967,7 +27967,7 @@
         <v>400</v>
       </c>
       <c r="V8" t="n">
-        <v>397.8918749462438</v>
+        <v>400</v>
       </c>
       <c r="W8" t="n">
         <v>400</v>
@@ -27998,10 +27998,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.5158377618198</v>
       </c>
       <c r="H9" t="n">
         <v>330.0076343562325</v>
@@ -28031,10 +28031,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>144.5243971659513</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>228.8626614203359</v>
+        <v>159.3848916320019</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
@@ -28046,13 +28046,13 @@
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>400</v>
+        <v>40.51066719152016</v>
       </c>
       <c r="W9" t="n">
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>308.3394196630687</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28065,28 +28065,28 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C10" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D10" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E10" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F10" t="n">
         <v>400</v>
       </c>
-      <c r="C10" t="n">
+      <c r="G10" t="n">
         <v>400</v>
-      </c>
-      <c r="D10" t="n">
-        <v>400</v>
-      </c>
-      <c r="E10" t="n">
-        <v>400</v>
-      </c>
-      <c r="F10" t="n">
-        <v>365.7622123898456</v>
-      </c>
-      <c r="G10" t="n">
-        <v>244.8563318579235</v>
       </c>
       <c r="H10" t="n">
         <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>170.9935867676593</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
         <v>22.00980129492416</v>
@@ -28095,7 +28095,7 @@
         <v>400</v>
       </c>
       <c r="L10" t="n">
-        <v>395.6653986495825</v>
+        <v>400</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28122,19 +28122,19 @@
         <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9481617662612</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>266.1308334902828</v>
       </c>
       <c r="W10" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28226,10 +28226,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>131.4624326227432</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>321</v>
@@ -28238,7 +28238,7 @@
         <v>321</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H12" t="n">
         <v>321</v>
@@ -28280,7 +28280,7 @@
         <v>321</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V12" t="n">
         <v>321</v>
@@ -28289,7 +28289,7 @@
         <v>321</v>
       </c>
       <c r="X12" t="n">
-        <v>321</v>
+        <v>131.4624326227432</v>
       </c>
       <c r="Y12" t="n">
         <v>321</v>
@@ -28317,10 +28317,10 @@
         <v>321</v>
       </c>
       <c r="G13" t="n">
-        <v>311.7961580087253</v>
+        <v>321</v>
       </c>
       <c r="H13" t="n">
-        <v>321</v>
+        <v>311.7961580087252</v>
       </c>
       <c r="I13" t="n">
         <v>321</v>
@@ -28396,10 +28396,10 @@
         <v>321</v>
       </c>
       <c r="G14" t="n">
+        <v>321</v>
+      </c>
+      <c r="H14" t="n">
         <v>319.7658196698623</v>
-      </c>
-      <c r="H14" t="n">
-        <v>321</v>
       </c>
       <c r="I14" t="n">
         <v>95.99142098921726</v>
@@ -28460,19 +28460,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E15" t="n">
         <v>321</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G15" t="n">
         <v>321</v>
@@ -28526,10 +28526,10 @@
         <v>321</v>
       </c>
       <c r="X15" t="n">
-        <v>131.4624326227434</v>
+        <v>131.4624326227432</v>
       </c>
       <c r="Y15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -28560,7 +28560,7 @@
         <v>321</v>
       </c>
       <c r="I16" t="n">
-        <v>321</v>
+        <v>311.7961580087252</v>
       </c>
       <c r="J16" t="n">
         <v>321</v>
@@ -28593,7 +28593,7 @@
         <v>321</v>
       </c>
       <c r="T16" t="n">
-        <v>311.7961580087252</v>
+        <v>321</v>
       </c>
       <c r="U16" t="n">
         <v>321</v>
@@ -28639,7 +28639,7 @@
         <v>321</v>
       </c>
       <c r="I17" t="n">
-        <v>95.99142098921726</v>
+        <v>94.75724065907951</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>161.5122727695135</v>
+        <v>162.7464530996513</v>
       </c>
       <c r="S17" t="n">
         <v>321</v>
@@ -28709,7 +28709,7 @@
         <v>321</v>
       </c>
       <c r="F18" t="n">
-        <v>131.4624326227433</v>
+        <v>321</v>
       </c>
       <c r="G18" t="n">
         <v>321</v>
@@ -28760,7 +28760,7 @@
         <v>321</v>
       </c>
       <c r="W18" t="n">
-        <v>321</v>
+        <v>131.4624326227434</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -28800,7 +28800,7 @@
         <v>321</v>
       </c>
       <c r="J19" t="n">
-        <v>311.7961580087251</v>
+        <v>321</v>
       </c>
       <c r="K19" t="n">
         <v>321</v>
@@ -28833,7 +28833,7 @@
         <v>321</v>
       </c>
       <c r="U19" t="n">
-        <v>321</v>
+        <v>311.7961580087252</v>
       </c>
       <c r="V19" t="n">
         <v>321</v>
@@ -28943,7 +28943,7 @@
         <v>321</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F21" t="n">
         <v>321</v>
@@ -28952,7 +28952,7 @@
         <v>321</v>
       </c>
       <c r="H21" t="n">
-        <v>131.4624326227432</v>
+        <v>321</v>
       </c>
       <c r="I21" t="n">
         <v>191.2806311743674</v>
@@ -28994,16 +28994,16 @@
         <v>321</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W21" t="n">
-        <v>321</v>
+        <v>131.4624326227434</v>
       </c>
       <c r="X21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -29037,7 +29037,7 @@
         <v>321</v>
       </c>
       <c r="J22" t="n">
-        <v>321</v>
+        <v>311.7961580087251</v>
       </c>
       <c r="K22" t="n">
         <v>321</v>
@@ -29079,7 +29079,7 @@
         <v>321</v>
       </c>
       <c r="X22" t="n">
-        <v>311.7961580087253</v>
+        <v>321</v>
       </c>
       <c r="Y22" t="n">
         <v>321</v>
@@ -29174,22 +29174,22 @@
         <v>321</v>
       </c>
       <c r="C24" t="n">
-        <v>321</v>
+        <v>131.4624326227433</v>
       </c>
       <c r="D24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>131.4624326227431</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>321</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I24" t="n">
         <v>191.2806311743674</v>
@@ -29228,10 +29228,10 @@
         <v>321</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W24" t="n">
         <v>321</v>
@@ -29274,7 +29274,7 @@
         <v>321</v>
       </c>
       <c r="J25" t="n">
-        <v>321</v>
+        <v>311.7961580087251</v>
       </c>
       <c r="K25" t="n">
         <v>321</v>
@@ -29307,7 +29307,7 @@
         <v>321</v>
       </c>
       <c r="U25" t="n">
-        <v>311.7961580087252</v>
+        <v>321</v>
       </c>
       <c r="V25" t="n">
         <v>321</v>
@@ -29329,25 +29329,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E26" t="n">
-        <v>320</v>
+        <v>315.8850196698622</v>
       </c>
       <c r="F26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I26" t="n">
         <v>95.99142098921726</v>
@@ -29380,25 +29380,25 @@
         <v>162.7464530996513</v>
       </c>
       <c r="S26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="U26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="W26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="27">
@@ -29408,25 +29408,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D27" t="n">
-        <v>142.4624326227432</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F27" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G27" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I27" t="n">
         <v>191.2806311743674</v>
@@ -29456,28 +29456,28 @@
         <v>77.25571792066825</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>131.4624326227433</v>
       </c>
       <c r="S27" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T27" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="U27" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V27" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X27" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y27" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="28">
@@ -29487,76 +29487,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G28" t="n">
-        <v>320.0000000000005</v>
+        <v>321</v>
       </c>
       <c r="H28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="S28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="U28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V28" t="n">
-        <v>320</v>
+        <v>311.7961580087251</v>
       </c>
       <c r="W28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="29">
@@ -29587,7 +29587,7 @@
         <v>321</v>
       </c>
       <c r="I29" t="n">
-        <v>90.87644065907821</v>
+        <v>95.99142098921726</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>162.7464530996513</v>
+        <v>157.6314727695134</v>
       </c>
       <c r="S29" t="n">
         <v>321</v>
@@ -29645,16 +29645,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>131.4624326227434</v>
       </c>
       <c r="F30" t="n">
         <v>321</v>
@@ -29666,7 +29666,7 @@
         <v>321</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>191.2806311743674</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29708,10 +29708,10 @@
         <v>321</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X30" t="n">
-        <v>1.743063797110551</v>
+        <v>321</v>
       </c>
       <c r="Y30" t="n">
         <v>321</v>
@@ -29736,7 +29736,7 @@
         <v>321</v>
       </c>
       <c r="F31" t="n">
-        <v>311.796158008725</v>
+        <v>321</v>
       </c>
       <c r="G31" t="n">
         <v>321</v>
@@ -29778,7 +29778,7 @@
         <v>321</v>
       </c>
       <c r="T31" t="n">
-        <v>321</v>
+        <v>311.7961580087251</v>
       </c>
       <c r="U31" t="n">
         <v>321</v>
@@ -29821,7 +29821,7 @@
         <v>321</v>
       </c>
       <c r="H32" t="n">
-        <v>315.8850196698609</v>
+        <v>315.8850196698622</v>
       </c>
       <c r="I32" t="n">
         <v>95.99142098921726</v>
@@ -29882,19 +29882,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>321</v>
+        <v>131.4624326227433</v>
       </c>
       <c r="D33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>321</v>
@@ -29930,7 +29930,7 @@
         <v>77.25571792066825</v>
       </c>
       <c r="R33" t="n">
-        <v>131.4624326227433</v>
+        <v>321</v>
       </c>
       <c r="S33" t="n">
         <v>321</v>
@@ -29939,7 +29939,7 @@
         <v>321</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V33" t="n">
         <v>321</v>
@@ -29951,7 +29951,7 @@
         <v>321</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="34">
@@ -29988,7 +29988,7 @@
         <v>321</v>
       </c>
       <c r="K34" t="n">
-        <v>311.7961580087249</v>
+        <v>321</v>
       </c>
       <c r="L34" t="n">
         <v>321</v>
@@ -30018,7 +30018,7 @@
         <v>321</v>
       </c>
       <c r="U34" t="n">
-        <v>321</v>
+        <v>311.7961580087251</v>
       </c>
       <c r="V34" t="n">
         <v>321</v>
@@ -30097,7 +30097,7 @@
         <v>345</v>
       </c>
       <c r="U35" t="n">
-        <v>345</v>
+        <v>341.5146196698618</v>
       </c>
       <c r="V35" t="n">
         <v>345</v>
@@ -30106,7 +30106,7 @@
         <v>345</v>
       </c>
       <c r="X35" t="n">
-        <v>341.5146196698619</v>
+        <v>345</v>
       </c>
       <c r="Y35" t="n">
         <v>345</v>
@@ -30119,25 +30119,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
         <v>345</v>
       </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>240.6098262234588</v>
+        <v>324.9888566297443</v>
       </c>
       <c r="H36" t="n">
-        <v>324.9181060543457</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>191.2806311743674</v>
@@ -30176,16 +30176,16 @@
         <v>345</v>
       </c>
       <c r="U36" t="n">
+        <v>238.2111728699728</v>
+      </c>
+      <c r="V36" t="n">
         <v>345</v>
       </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
       <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
         <v>345</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>345</v>
@@ -30198,7 +30198,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>287.1138003370787</v>
+        <v>345</v>
       </c>
       <c r="C37" t="n">
         <v>345</v>
@@ -30222,13 +30222,13 @@
         <v>345</v>
       </c>
       <c r="J37" t="n">
-        <v>195.2970909935997</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>215.4024131454054</v>
       </c>
       <c r="L37" t="n">
-        <v>345</v>
+        <v>329.9813002889267</v>
       </c>
       <c r="M37" t="n">
         <v>345</v>
@@ -30255,7 +30255,7 @@
         <v>345</v>
       </c>
       <c r="U37" t="n">
-        <v>150.9240634056055</v>
+        <v>245.8190072968194</v>
       </c>
       <c r="V37" t="n">
         <v>345</v>
@@ -30267,7 +30267,7 @@
         <v>345</v>
       </c>
       <c r="Y37" t="n">
-        <v>287.4653528494624</v>
+        <v>345</v>
       </c>
     </row>
     <row r="38">
@@ -30295,7 +30295,7 @@
         <v>345</v>
       </c>
       <c r="H38" t="n">
-        <v>345</v>
+        <v>341.5146196698617</v>
       </c>
       <c r="I38" t="n">
         <v>95.99142098921726</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>159.2610727695133</v>
+        <v>162.7464530996513</v>
       </c>
       <c r="S38" t="n">
         <v>345</v>
@@ -30356,13 +30356,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="C39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>342.6720972219126</v>
@@ -30377,7 +30377,7 @@
         <v>324.9181060543457</v>
       </c>
       <c r="I39" t="n">
-        <v>101.5378431059588</v>
+        <v>191.2806311743674</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30407,7 +30407,7 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>345</v>
+        <v>255.2572119315459</v>
       </c>
       <c r="T39" t="n">
         <v>345</v>
@@ -30422,7 +30422,7 @@
         <v>345</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="Y39" t="n">
         <v>345</v>
@@ -30438,7 +30438,7 @@
         <v>345</v>
       </c>
       <c r="C40" t="n">
-        <v>272.7252466480447</v>
+        <v>345</v>
       </c>
       <c r="D40" t="n">
         <v>345</v>
@@ -30453,16 +30453,16 @@
         <v>345</v>
       </c>
       <c r="H40" t="n">
-        <v>223.1756834786678</v>
+        <v>345</v>
       </c>
       <c r="I40" t="n">
         <v>345</v>
       </c>
       <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>345</v>
-      </c>
-      <c r="K40" t="n">
-        <v>233.7959302754077</v>
       </c>
       <c r="L40" t="n">
         <v>345</v>
@@ -30489,10 +30489,10 @@
         <v>345</v>
       </c>
       <c r="T40" t="n">
-        <v>207.3355501128151</v>
+        <v>345</v>
       </c>
       <c r="U40" t="n">
-        <v>345</v>
+        <v>247.0324105149352</v>
       </c>
       <c r="V40" t="n">
         <v>199.1703102162162</v>
@@ -30596,7 +30596,7 @@
         <v>321</v>
       </c>
       <c r="C42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>321</v>
@@ -30605,13 +30605,13 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H42" t="n">
-        <v>321</v>
+        <v>131.8362718375936</v>
       </c>
       <c r="I42" t="n">
         <v>191.2806311743674</v>
@@ -30638,7 +30638,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>77.25571792066825</v>
       </c>
       <c r="R42" t="n">
         <v>321</v>
@@ -30647,7 +30647,7 @@
         <v>321</v>
       </c>
       <c r="T42" t="n">
-        <v>209.0919897582619</v>
+        <v>321</v>
       </c>
       <c r="U42" t="n">
         <v>321</v>
@@ -30656,7 +30656,7 @@
         <v>321</v>
       </c>
       <c r="W42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>321</v>
@@ -30696,7 +30696,7 @@
         <v>321</v>
       </c>
       <c r="J43" t="n">
-        <v>321</v>
+        <v>311.7961580087251</v>
       </c>
       <c r="K43" t="n">
         <v>321</v>
@@ -30726,7 +30726,7 @@
         <v>321</v>
       </c>
       <c r="T43" t="n">
-        <v>311.7961580087251</v>
+        <v>321</v>
       </c>
       <c r="U43" t="n">
         <v>321</v>
@@ -30830,7 +30830,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C45" t="n">
         <v>321</v>
@@ -30839,7 +30839,7 @@
         <v>321</v>
       </c>
       <c r="E45" t="n">
-        <v>131.8362718375936</v>
+        <v>321</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -30848,10 +30848,10 @@
         <v>321</v>
       </c>
       <c r="H45" t="n">
-        <v>321</v>
+        <v>79.37262093262947</v>
       </c>
       <c r="I45" t="n">
-        <v>191.2806311743674</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30875,10 +30875,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>77.25571792064619</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>321</v>
@@ -30899,7 +30899,7 @@
         <v>321</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="46">
@@ -30933,40 +30933,40 @@
         <v>321</v>
       </c>
       <c r="J46" t="n">
+        <v>321</v>
+      </c>
+      <c r="K46" t="n">
+        <v>321</v>
+      </c>
+      <c r="L46" t="n">
+        <v>321</v>
+      </c>
+      <c r="M46" t="n">
+        <v>321</v>
+      </c>
+      <c r="N46" t="n">
+        <v>321</v>
+      </c>
+      <c r="O46" t="n">
+        <v>321</v>
+      </c>
+      <c r="P46" t="n">
+        <v>321</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>321</v>
+      </c>
+      <c r="R46" t="n">
+        <v>321</v>
+      </c>
+      <c r="S46" t="n">
+        <v>321</v>
+      </c>
+      <c r="T46" t="n">
+        <v>321</v>
+      </c>
+      <c r="U46" t="n">
         <v>311.7961580087251</v>
-      </c>
-      <c r="K46" t="n">
-        <v>321</v>
-      </c>
-      <c r="L46" t="n">
-        <v>321</v>
-      </c>
-      <c r="M46" t="n">
-        <v>321</v>
-      </c>
-      <c r="N46" t="n">
-        <v>321</v>
-      </c>
-      <c r="O46" t="n">
-        <v>321</v>
-      </c>
-      <c r="P46" t="n">
-        <v>321</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>321</v>
-      </c>
-      <c r="R46" t="n">
-        <v>321</v>
-      </c>
-      <c r="S46" t="n">
-        <v>321</v>
-      </c>
-      <c r="T46" t="n">
-        <v>321</v>
-      </c>
-      <c r="U46" t="n">
-        <v>321</v>
       </c>
       <c r="V46" t="n">
         <v>321</v>
@@ -31091,49 +31091,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4180904522613062</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H2" t="n">
-        <v>4.281768844221103</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I2" t="n">
-        <v>16.11843216080402</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J2" t="n">
-        <v>35.48490452261307</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K2" t="n">
-        <v>53.18267336683417</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>65.97780904522614</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M2" t="n">
-        <v>73.41302512562814</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N2" t="n">
-        <v>74.60092462311559</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O2" t="n">
-        <v>70.44353768844221</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P2" t="n">
-        <v>60.12192964824121</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q2" t="n">
-        <v>45.14906532663316</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R2" t="n">
-        <v>26.2628743718593</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S2" t="n">
-        <v>9.527236180904525</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T2" t="n">
-        <v>1.830190954773869</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03344723618090449</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31170,49 +31170,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2236981132075472</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H3" t="n">
-        <v>2.16045283018868</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I3" t="n">
-        <v>7.701886792452831</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J3" t="n">
-        <v>21.13456603773585</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K3" t="n">
-        <v>36.12233962264151</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L3" t="n">
-        <v>48.57094339622642</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M3" t="n">
-        <v>56.67999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>58.18015094339623</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O3" t="n">
-        <v>53.22347169811321</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P3" t="n">
-        <v>42.7165283018868</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.55486792452831</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R3" t="n">
-        <v>13.88890566037736</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S3" t="n">
-        <v>4.155094339622639</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9016603773584903</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01471698113207548</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,49 +31249,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1875409836065574</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H4" t="n">
-        <v>1.667409836065575</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I4" t="n">
-        <v>5.639868852459018</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J4" t="n">
-        <v>13.25914754098361</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K4" t="n">
-        <v>21.78885245901639</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L4" t="n">
-        <v>27.88222950819672</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M4" t="n">
-        <v>29.39790163934425</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N4" t="n">
-        <v>28.69888524590166</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O4" t="n">
-        <v>26.5080655737705</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P4" t="n">
-        <v>22.68222950819671</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.704</v>
+        <v>15.553</v>
       </c>
       <c r="R4" t="n">
-        <v>8.432524590163931</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S4" t="n">
-        <v>3.268327868852458</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8013114754098358</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01022950819672132</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -34743,25 +34743,25 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
+        <v>0.1006972724976123</v>
+      </c>
+      <c r="K2" t="n">
+        <v>52.67130150753769</v>
+      </c>
+      <c r="L2" t="n">
+        <v>246.8601159786807</v>
+      </c>
+      <c r="M2" t="n">
         <v>374</v>
       </c>
-      <c r="K2" t="n">
-        <v>373.9999999999999</v>
-      </c>
-      <c r="L2" t="n">
-        <v>65.97780904522619</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1956681143497576</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>292.7154117293131</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q2" t="n">
         <v>374</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>146.3431722754116</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K3" t="n">
-        <v>227.2261942634328</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L3" t="n">
-        <v>322.6623187449134</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M3" t="n">
-        <v>140.7874761356804</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>192.8067010520511</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O3" t="n">
-        <v>294.6804936008596</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P3" t="n">
-        <v>156.38253281654</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34892,22 +34892,22 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>155.1436681420765</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H4" t="n">
-        <v>172.896283734447</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I4" t="n">
-        <v>229.0064132323407</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>133.2680786578734</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L4" t="n">
-        <v>4.33460135041755</v>
+        <v>4.066502989761812</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,10 +34928,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>40.86342193648883</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>35.01572123559315</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -34943,7 +34943,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>74.04012452058966</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4418982775227391</v>
+        <v>374</v>
       </c>
       <c r="K5" t="n">
+        <v>373.9999999999999</v>
+      </c>
+      <c r="L5" t="n">
         <v>374</v>
       </c>
-      <c r="L5" t="n">
-        <v>65.97780904522614</v>
-      </c>
       <c r="M5" t="n">
-        <v>232.6343119585803</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>374</v>
+        <v>0.1956681143497723</v>
       </c>
       <c r="P5" t="n">
         <v>59.8348696075598</v>
       </c>
       <c r="Q5" t="n">
-        <v>374</v>
+        <v>298.8583511669793</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,7 +35114,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
         <v>127.2747533519553</v>
@@ -35126,13 +35126,13 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>5.706593770760218</v>
       </c>
       <c r="G7" t="n">
-        <v>155.1436681420765</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>172.896283734447</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -35144,7 +35144,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4.334601350417529</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,13 +35165,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.89484816599702</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0518382337388</v>
       </c>
       <c r="V7" t="n">
         <v>200.8296897837838</v>
@@ -35180,7 +35180,7 @@
         <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>21.31444081211666</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
         <v>112.5346471505376</v>
@@ -35217,22 +35217,22 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
+        <v>0.4418982775227391</v>
+      </c>
+      <c r="K8" t="n">
         <v>374</v>
-      </c>
-      <c r="K8" t="n">
-        <v>373.9999999999999</v>
       </c>
       <c r="L8" t="n">
         <v>374</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>298.4164528894565</v>
       </c>
       <c r="N8" t="n">
-        <v>298.8583511669793</v>
+        <v>374</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1956681143497576</v>
+        <v>0.1956681143497723</v>
       </c>
       <c r="P8" t="n">
         <v>59.8348696075598</v>
@@ -35305,13 +35305,13 @@
         <v>322.6623187449134</v>
       </c>
       <c r="M9" t="n">
-        <v>140.7874761356804</v>
+        <v>143.6300421645043</v>
       </c>
       <c r="N9" t="n">
         <v>192.8067010520511</v>
       </c>
       <c r="O9" t="n">
-        <v>294.6804936008596</v>
+        <v>291.8379275720357</v>
       </c>
       <c r="P9" t="n">
         <v>156.38253281654</v>
@@ -35351,28 +35351,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>91.3793564221036</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>155.1436681420765</v>
       </c>
       <c r="H10" t="n">
         <v>172.896283734447</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>229.0064132323407</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -35381,7 +35381,7 @@
         <v>133.2680786578733</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.334601350417529</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35408,19 +35408,19 @@
         <v>190.7767449691521</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0518382337388</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>66.96052327406666</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35457,16 +35457,16 @@
         <v>514.3408810948353</v>
       </c>
       <c r="K11" t="n">
+        <v>178.4687788944724</v>
+      </c>
+      <c r="L11" t="n">
+        <v>221.4063015075377</v>
+      </c>
+      <c r="M11" t="n">
+        <v>44.40993484306512</v>
+      </c>
+      <c r="N11" t="n">
         <v>649</v>
-      </c>
-      <c r="L11" t="n">
-        <v>649</v>
-      </c>
-      <c r="M11" t="n">
-        <v>389.8242484082692</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>166.1443867073146</v>
@@ -35475,7 +35475,7 @@
         <v>201.4682615673588</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>594.5392331631938</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35603,10 +35603,10 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G13" t="n">
-        <v>67.38162942949037</v>
+        <v>76.58547142076505</v>
       </c>
       <c r="H13" t="n">
-        <v>97.82431652133221</v>
+        <v>88.62047453005744</v>
       </c>
       <c r="I13" t="n">
         <v>163.2926427405375</v>
@@ -35694,25 +35694,25 @@
         <v>84.03614450867852</v>
       </c>
       <c r="K14" t="n">
-        <v>178.4687788944724</v>
+        <v>649</v>
       </c>
       <c r="L14" t="n">
+        <v>221.4063015075377</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4.183450323694275</v>
+      </c>
+      <c r="N14" t="n">
         <v>649</v>
       </c>
-      <c r="M14" t="n">
-        <v>649</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
       <c r="O14" t="n">
-        <v>360.2728543746268</v>
+        <v>166.1443867073146</v>
       </c>
       <c r="P14" t="n">
-        <v>649</v>
+        <v>201.4682615673588</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>594.5392331631938</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35846,7 +35846,7 @@
         <v>97.82431652133221</v>
       </c>
       <c r="I16" t="n">
-        <v>163.2926427405375</v>
+        <v>154.0888007492626</v>
       </c>
       <c r="J16" t="n">
         <v>330.2256905083545</v>
@@ -35879,7 +35879,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>104.4606078959101</v>
+        <v>113.6644498871849</v>
       </c>
       <c r="U16" t="n">
         <v>170.0759365943945</v>
@@ -35931,16 +35931,16 @@
         <v>514.3408810948353</v>
       </c>
       <c r="K17" t="n">
+        <v>178.4687788944724</v>
+      </c>
+      <c r="L17" t="n">
+        <v>649.0000000000001</v>
+      </c>
+      <c r="M17" t="n">
+        <v>211.3554695137966</v>
+      </c>
+      <c r="N17" t="n">
         <v>649</v>
-      </c>
-      <c r="L17" t="n">
-        <v>649</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>166.1443867073146</v>
@@ -35949,7 +35949,7 @@
         <v>201.4682615673588</v>
       </c>
       <c r="Q17" t="n">
-        <v>389.8242484082692</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36086,7 +36086,7 @@
         <v>163.2926427405375</v>
       </c>
       <c r="J19" t="n">
-        <v>321.0218485170797</v>
+        <v>330.2256905083545</v>
       </c>
       <c r="K19" t="n">
         <v>105.5975868545946</v>
@@ -36119,7 +36119,7 @@
         <v>113.6644498871849</v>
       </c>
       <c r="U19" t="n">
-        <v>170.0759365943945</v>
+        <v>160.8720946031198</v>
       </c>
       <c r="V19" t="n">
         <v>121.8296897837838</v>
@@ -36165,7 +36165,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>514.3408810948353</v>
+        <v>84.03614450867852</v>
       </c>
       <c r="K20" t="n">
         <v>178.4687788944724</v>
@@ -36177,16 +36177,16 @@
         <v>649</v>
       </c>
       <c r="N20" t="n">
-        <v>44.40993484306523</v>
+        <v>586.3982912997304</v>
       </c>
       <c r="O20" t="n">
-        <v>166.1443867073146</v>
+        <v>649</v>
       </c>
       <c r="P20" t="n">
         <v>201.4682615673588</v>
       </c>
       <c r="Q20" t="n">
-        <v>594.5392331631938</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36314,7 +36314,7 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G22" t="n">
-        <v>76.58547142076506</v>
+        <v>76.58547142076505</v>
       </c>
       <c r="H22" t="n">
         <v>97.82431652133221</v>
@@ -36323,7 +36323,7 @@
         <v>163.2926427405375</v>
       </c>
       <c r="J22" t="n">
-        <v>330.2256905083545</v>
+        <v>321.0218485170797</v>
       </c>
       <c r="K22" t="n">
         <v>105.5975868545946</v>
@@ -36365,7 +36365,7 @@
         <v>94.62719016129032</v>
       </c>
       <c r="X22" t="n">
-        <v>64.35251257861778</v>
+        <v>73.55635456989245</v>
       </c>
       <c r="Y22" t="n">
         <v>33.53464715053764</v>
@@ -36408,22 +36408,22 @@
         <v>178.4687788944724</v>
       </c>
       <c r="L23" t="n">
-        <v>649.0000000000001</v>
+        <v>221.4063015075377</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>191.4174295736177</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O23" t="n">
         <v>166.1443867073146</v>
       </c>
       <c r="P23" t="n">
-        <v>467.2844979179615</v>
+        <v>649</v>
       </c>
       <c r="Q23" t="n">
-        <v>594.5392331631938</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36560,7 +36560,7 @@
         <v>163.2926427405375</v>
       </c>
       <c r="J25" t="n">
-        <v>330.2256905083545</v>
+        <v>321.0218485170797</v>
       </c>
       <c r="K25" t="n">
         <v>105.5975868545946</v>
@@ -36593,7 +36593,7 @@
         <v>113.6644498871849</v>
       </c>
       <c r="U25" t="n">
-        <v>160.8720946031198</v>
+        <v>170.0759365943945</v>
       </c>
       <c r="V25" t="n">
         <v>121.8296897837838</v>
@@ -36639,28 +36639,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>514.3408810948353</v>
+        <v>84.03614450867852</v>
       </c>
       <c r="K26" t="n">
-        <v>178.4687788944724</v>
+        <v>650</v>
       </c>
       <c r="L26" t="n">
-        <v>650.0000000000003</v>
+        <v>649.9999999999999</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>650.0000000000001</v>
+        <v>227.5493477908281</v>
       </c>
       <c r="O26" t="n">
-        <v>379.459452180708</v>
+        <v>166.1443867073146</v>
       </c>
       <c r="P26" t="n">
         <v>201.4682615673588</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>594.5392331631938</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36773,34 +36773,34 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32.88619966292134</v>
+        <v>33.88619966292134</v>
       </c>
       <c r="C28" t="n">
-        <v>47.27475335195533</v>
+        <v>48.27475335195533</v>
       </c>
       <c r="D28" t="n">
-        <v>34.46378194444452</v>
+        <v>35.46378194444452</v>
       </c>
       <c r="E28" t="n">
-        <v>39.01909516304346</v>
+        <v>40.01909516304346</v>
       </c>
       <c r="F28" t="n">
-        <v>45.61714403225807</v>
+        <v>46.61714403225807</v>
       </c>
       <c r="G28" t="n">
-        <v>75.5854714207655</v>
+        <v>76.58547142076506</v>
       </c>
       <c r="H28" t="n">
-        <v>96.82431652133221</v>
+        <v>97.82431652133221</v>
       </c>
       <c r="I28" t="n">
-        <v>162.2926427405375</v>
+        <v>163.2926427405375</v>
       </c>
       <c r="J28" t="n">
-        <v>329.2256905083545</v>
+        <v>330.2256905083545</v>
       </c>
       <c r="K28" t="n">
-        <v>104.5975868545946</v>
+        <v>105.5975868545946</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -36827,22 +36827,22 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>112.6644498871849</v>
+        <v>113.6644498871849</v>
       </c>
       <c r="U28" t="n">
-        <v>169.0759365943945</v>
+        <v>170.0759365943945</v>
       </c>
       <c r="V28" t="n">
-        <v>120.8296897837838</v>
+        <v>112.6258477925089</v>
       </c>
       <c r="W28" t="n">
-        <v>93.62719016129032</v>
+        <v>94.62719016129032</v>
       </c>
       <c r="X28" t="n">
-        <v>72.55635456989245</v>
+        <v>73.55635456989245</v>
       </c>
       <c r="Y28" t="n">
-        <v>32.53464715053764</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
     <row r="29">
@@ -36876,28 +36876,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>514.3408810948353</v>
+        <v>84.03614450867852</v>
       </c>
       <c r="K29" t="n">
         <v>178.4687788944724</v>
       </c>
       <c r="L29" t="n">
-        <v>650.0000000000003</v>
+        <v>221.4063015075377</v>
       </c>
       <c r="M29" t="n">
-        <v>414.7833270407523</v>
+        <v>650</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="O29" t="n">
         <v>166.1443867073146</v>
       </c>
       <c r="P29" t="n">
-        <v>650.0000000000003</v>
+        <v>201.4682615673588</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>422.2135005520117</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37022,7 +37022,7 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F31" t="n">
-        <v>37.41330204098307</v>
+        <v>46.61714403225807</v>
       </c>
       <c r="G31" t="n">
         <v>76.58547142076506</v>
@@ -37064,7 +37064,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>113.6644498871849</v>
+        <v>104.46060789591</v>
       </c>
       <c r="U31" t="n">
         <v>170.0759365943945</v>
@@ -37116,22 +37116,22 @@
         <v>84.03614450867852</v>
       </c>
       <c r="K32" t="n">
-        <v>650.0000000000002</v>
+        <v>178.4687788944724</v>
       </c>
       <c r="L32" t="n">
         <v>221.4063015075377</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>477.6742673888178</v>
       </c>
       <c r="N32" t="n">
-        <v>207.6113078506498</v>
+        <v>650</v>
       </c>
       <c r="O32" t="n">
         <v>166.1443867073146</v>
       </c>
       <c r="P32" t="n">
-        <v>650.0000000000005</v>
+        <v>201.4682615673588</v>
       </c>
       <c r="Q32" t="n">
         <v>594.5392331631938</v>
@@ -37274,7 +37274,7 @@
         <v>330.2256905083545</v>
       </c>
       <c r="K34" t="n">
-        <v>96.39374486331957</v>
+        <v>105.5975868545946</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -37304,7 +37304,7 @@
         <v>113.6644498871849</v>
       </c>
       <c r="U34" t="n">
-        <v>170.0759365943945</v>
+        <v>160.8720946031196</v>
       </c>
       <c r="V34" t="n">
         <v>121.8296897837838</v>
@@ -37356,22 +37356,22 @@
         <v>178.4687788944724</v>
       </c>
       <c r="L35" t="n">
-        <v>221.4063015075377</v>
+        <v>473.1349535747011</v>
       </c>
       <c r="M35" t="n">
-        <v>453.1969136345223</v>
+        <v>563</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>563</v>
       </c>
       <c r="O35" t="n">
         <v>166.1443867073146</v>
       </c>
       <c r="P35" t="n">
-        <v>563</v>
+        <v>201.4682615673588</v>
       </c>
       <c r="Q35" t="n">
-        <v>563</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37441,10 +37441,10 @@
         <v>277.1550421645043</v>
       </c>
       <c r="N36" t="n">
-        <v>329.8657104860133</v>
+        <v>329.484280820826</v>
       </c>
       <c r="O36" t="n">
-        <v>419.6812809168043</v>
+        <v>420.0627105819917</v>
       </c>
       <c r="P36" t="n">
         <v>257.0128158354079</v>
@@ -37484,7 +37484,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>57.88619966292134</v>
       </c>
       <c r="C37" t="n">
         <v>72.27475335195533</v>
@@ -37499,7 +37499,7 @@
         <v>70.61714403225807</v>
       </c>
       <c r="G37" t="n">
-        <v>100.585471420765</v>
+        <v>100.5854714207651</v>
       </c>
       <c r="H37" t="n">
         <v>121.8243165213322</v>
@@ -37508,13 +37508,13 @@
         <v>187.2926427405375</v>
       </c>
       <c r="J37" t="n">
-        <v>204.5227815019543</v>
+        <v>9.225690508354518</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>15.0186997110733</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37541,7 +37541,7 @@
         <v>137.6644498871849</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>94.8949438912139</v>
       </c>
       <c r="V37" t="n">
         <v>145.8296897837838</v>
@@ -37553,7 +37553,7 @@
         <v>97.55635456989245</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>57.53464715053764</v>
       </c>
     </row>
     <row r="38">
@@ -37587,16 +37587,16 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>172.639876977852</v>
+        <v>84.03614450867852</v>
       </c>
       <c r="K38" t="n">
+        <v>178.4687788944724</v>
+      </c>
+      <c r="L38" t="n">
+        <v>473.1349535747011</v>
+      </c>
+      <c r="M38" t="n">
         <v>563</v>
-      </c>
-      <c r="L38" t="n">
-        <v>563</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>563</v>
@@ -37672,7 +37672,7 @@
         <v>312.3220904898479</v>
       </c>
       <c r="L39" t="n">
-        <v>436.7028230419905</v>
+        <v>436.7028230420369</v>
       </c>
       <c r="M39" t="n">
         <v>277.1550421645043</v>
@@ -37724,7 +37724,7 @@
         <v>57.88619966292134</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>72.27475335195533</v>
       </c>
       <c r="D40" t="n">
         <v>59.46378194444452</v>
@@ -37739,16 +37739,16 @@
         <v>100.585471420765</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>121.8243165213322</v>
       </c>
       <c r="I40" t="n">
         <v>187.2926427405375</v>
       </c>
       <c r="J40" t="n">
-        <v>354.2256905083545</v>
+        <v>9.225690508354518</v>
       </c>
       <c r="K40" t="n">
-        <v>18.39351713000233</v>
+        <v>129.5975868545946</v>
       </c>
       <c r="L40" t="n">
         <v>15.0186997110733</v>
@@ -37775,10 +37775,10 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>137.6644498871849</v>
       </c>
       <c r="U40" t="n">
-        <v>194.0759365943945</v>
+        <v>96.10834710932974</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -37830,13 +37830,13 @@
         <v>178.4687788944724</v>
       </c>
       <c r="L41" t="n">
+        <v>221.4063015075377</v>
+      </c>
+      <c r="M41" t="n">
         <v>563</v>
       </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
       <c r="N41" t="n">
-        <v>473.134953574701</v>
+        <v>251.7286520671635</v>
       </c>
       <c r="O41" t="n">
         <v>166.1443867073146</v>
@@ -37982,7 +37982,7 @@
         <v>163.2926427405375</v>
       </c>
       <c r="J43" t="n">
-        <v>330.2256905083545</v>
+        <v>321.0218485170797</v>
       </c>
       <c r="K43" t="n">
         <v>105.5975868545946</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>104.46060789591</v>
+        <v>113.6644498871849</v>
       </c>
       <c r="U43" t="n">
         <v>170.0759365943945</v>
@@ -38073,16 +38073,16 @@
         <v>563</v>
       </c>
       <c r="N44" t="n">
-        <v>417.8730387744779</v>
+        <v>563</v>
       </c>
       <c r="O44" t="n">
-        <v>563</v>
+        <v>166.1443867073146</v>
       </c>
       <c r="P44" t="n">
         <v>201.4682615673588</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>251.7286520671637</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38152,10 +38152,10 @@
         <v>277.1550421645043</v>
       </c>
       <c r="N45" t="n">
-        <v>329.8657104860133</v>
+        <v>329.484280820826</v>
       </c>
       <c r="O45" t="n">
-        <v>419.6812809168268</v>
+        <v>420.0627105819917</v>
       </c>
       <c r="P45" t="n">
         <v>257.0128158354079</v>
@@ -38219,7 +38219,7 @@
         <v>163.2926427405375</v>
       </c>
       <c r="J46" t="n">
-        <v>321.0218485170797</v>
+        <v>330.2256905083545</v>
       </c>
       <c r="K46" t="n">
         <v>105.5975868545946</v>
@@ -38252,7 +38252,7 @@
         <v>113.6644498871849</v>
       </c>
       <c r="U46" t="n">
-        <v>170.0759365943945</v>
+        <v>160.8720946031196</v>
       </c>
       <c r="V46" t="n">
         <v>121.8296897837838</v>
